--- a/courses/Reg/DailyRecord.xlsx
+++ b/courses/Reg/DailyRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbarreto\Documents\GitHub\homepage\courses\Reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D02C3E-F597-45ED-AE83-4E36988C8945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72612D85-222D-4E7C-8447-13E7512799B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="254">
   <si>
     <t>Grade</t>
   </si>
@@ -341,9 +341,6 @@
   </si>
   <si>
     <t>11.Polling.doc</t>
-  </si>
-  <si>
-    <t>Blank file, completed version Polling2025.xls</t>
   </si>
   <si>
     <t>12.Unem, 13.Search, 2 questions</t>
@@ -924,6 +921,21 @@
   </si>
   <si>
     <t>https://depauw-edu.zoom.us/rec/share/XKeJyvUQqDwX_QOhT5GXLN3-kxlo8bg8kovnU5RiGcXok5aNCuZdj8RloVGeBH66.beRU6aLw7nUkbqTe</t>
+  </si>
+  <si>
+    <t>Passcode: 4G01d%Hz</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/lhHiHPHjmcnsDk4e1ASO8Ixsl8TI6dr2aroAu9UqHX4RaOIon1N9dfHp7597Q7VI.k11-6KZaV0KX79Om</t>
+  </si>
+  <si>
+    <t>Blank file, completed version 10.PollingPostClass.xls</t>
+  </si>
+  <si>
+    <t>Passcode: CY6ZNa=W</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/YgPD9M5qq2ZoYC1bbprhEdyy3yMi8x5V7X19fFkJlalCd04Ba-6DF1Tw5ZnxbBAg.l2hOVlM_9gV7FShe</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1563,7 @@
     </row>
     <row r="2" spans="1:18" ht="13.2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1559,11 +1571,11 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16.2" thickBot="1">
@@ -1583,20 +1595,20 @@
         <v>12</v>
       </c>
       <c r="F4" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>159</v>
-      </c>
       <c r="H4" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J4" s="27"/>
       <c r="L4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.6">
@@ -1611,25 +1623,25 @@
         <v>Mon</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
         <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I5" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="J5" t="s">
         <v>165</v>
-      </c>
-      <c r="J5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.6">
@@ -1651,22 +1663,22 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G6" t="s">
         <v>51</v>
       </c>
       <c r="H6" t="s">
+        <v>218</v>
+      </c>
+      <c r="I6" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="J6" t="s">
         <v>220</v>
       </c>
-      <c r="J6" t="s">
-        <v>221</v>
-      </c>
       <c r="L6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="24">
@@ -1688,22 +1700,22 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G7" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.6">
@@ -1725,7 +1737,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G8" t="s">
         <v>53</v>
@@ -1734,13 +1746,13 @@
         <v>54</v>
       </c>
       <c r="I8" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="J8" t="s">
         <v>225</v>
       </c>
-      <c r="J8" t="s">
-        <v>226</v>
-      </c>
       <c r="L8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.6">
@@ -1771,19 +1783,19 @@
         <v>57</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L9" t="s">
+        <v>170</v>
+      </c>
+      <c r="M9" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="R9" t="s">
         <v>172</v>
-      </c>
-      <c r="R9" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.6">
@@ -1802,7 +1814,7 @@
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
@@ -1811,19 +1823,19 @@
         <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L10" t="s">
+        <v>208</v>
+      </c>
+      <c r="M10" s="24" t="s">
         <v>209</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.6">
@@ -1851,16 +1863,16 @@
         <v>64</v>
       </c>
       <c r="H11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.6">
@@ -1879,25 +1891,25 @@
         <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G12" t="s">
         <v>66</v>
       </c>
       <c r="H12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="J12" t="s">
         <v>242</v>
       </c>
-      <c r="I12" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="J12" t="s">
-        <v>243</v>
-      </c>
       <c r="L12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.6">
@@ -1916,7 +1928,7 @@
         <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -1928,13 +1940,13 @@
         <v>70</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.6">
@@ -1964,8 +1976,14 @@
       <c r="H14" t="s">
         <v>74</v>
       </c>
+      <c r="I14" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="J14" t="s">
+        <v>249</v>
+      </c>
       <c r="L14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.6">
@@ -1993,10 +2011,16 @@
         <v>77</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>251</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="J15" t="s">
+        <v>252</v>
       </c>
       <c r="L15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.6">
@@ -2018,16 +2042,16 @@
         <v>24</v>
       </c>
       <c r="F16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" t="s">
         <v>79</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>80</v>
       </c>
-      <c r="H16" t="s">
-        <v>81</v>
-      </c>
       <c r="L16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6">
@@ -2043,19 +2067,16 @@
         <v>Mon</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
       <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
         <v>83</v>
-      </c>
-      <c r="G17" t="s">
-        <v>84</v>
-      </c>
-      <c r="L17" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6">
@@ -2074,14 +2095,14 @@
         <v>1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G18" s="6"/>
       <c r="L18" t="s">
+        <v>180</v>
+      </c>
+      <c r="M18" t="s">
         <v>181</v>
-      </c>
-      <c r="M18" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6">
@@ -2097,19 +2118,22 @@
         <v>Fri</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
         <v>86</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>87</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>88</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>89</v>
       </c>
-      <c r="H19" t="s">
-        <v>90</v>
+      <c r="L19" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6">
@@ -2128,16 +2152,16 @@
         <v>25</v>
       </c>
       <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
         <v>91</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>92</v>
       </c>
-      <c r="G20" t="s">
-        <v>93</v>
-      </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6">
@@ -2153,22 +2177,22 @@
         <v>Wed</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
         <v>95</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>96</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>97</v>
       </c>
-      <c r="G21" t="s">
-        <v>98</v>
-      </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6">
@@ -2187,22 +2211,22 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
         <v>99</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>100</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>101</v>
       </c>
-      <c r="H22" t="s">
-        <v>102</v>
-      </c>
       <c r="L22" t="s">
+        <v>184</v>
+      </c>
+      <c r="M22" t="s">
         <v>185</v>
-      </c>
-      <c r="M22" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6">
@@ -2221,19 +2245,19 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" t="s">
         <v>118</v>
       </c>
-      <c r="F23" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>119</v>
       </c>
-      <c r="H23" t="s">
-        <v>120</v>
-      </c>
       <c r="L23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6">
@@ -2252,16 +2276,16 @@
         <v>28</v>
       </c>
       <c r="F24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6">
@@ -2280,16 +2304,16 @@
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6">
@@ -2308,16 +2332,16 @@
         <v>30</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6">
@@ -2336,19 +2360,19 @@
         <v>32</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" t="s">
         <v>104</v>
       </c>
-      <c r="F27" t="s">
-        <v>155</v>
-      </c>
-      <c r="G27" t="s">
-        <v>105</v>
-      </c>
       <c r="H27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6">
@@ -2367,16 +2391,16 @@
         <v>45</v>
       </c>
       <c r="E28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" t="s">
         <v>106</v>
       </c>
-      <c r="F28" t="s">
-        <v>156</v>
-      </c>
-      <c r="G28" t="s">
-        <v>107</v>
-      </c>
       <c r="H28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6">
@@ -2407,7 +2431,7 @@
         <v>31</v>
       </c>
       <c r="L30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6">
@@ -2424,10 +2448,10 @@
         <v>31</v>
       </c>
       <c r="L31" t="s">
+        <v>192</v>
+      </c>
+      <c r="M31" t="s">
         <v>193</v>
-      </c>
-      <c r="M31" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.6">
@@ -2446,19 +2470,19 @@
         <v>33</v>
       </c>
       <c r="E32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.6">
@@ -2477,19 +2501,19 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" t="s">
         <v>128</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>129</v>
       </c>
-      <c r="G33" t="s">
-        <v>130</v>
-      </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.6">
@@ -2508,19 +2532,19 @@
         <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s">
+        <v>196</v>
+      </c>
+      <c r="M34" t="s">
         <v>197</v>
-      </c>
-      <c r="M34" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15.6">
@@ -2539,19 +2563,19 @@
         <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s">
+        <v>198</v>
+      </c>
+      <c r="M35" t="s">
         <v>199</v>
-      </c>
-      <c r="M35" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15.6">
@@ -2567,13 +2591,13 @@
         <v>Wed</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="16.2" thickBot="1">
@@ -2598,13 +2622,13 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L37" t="s">
+        <v>200</v>
+      </c>
+      <c r="M37" t="s">
         <v>201</v>
-      </c>
-      <c r="M37" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.6">
@@ -2623,17 +2647,17 @@
         <v>10</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" t="s">
         <v>36</v>
       </c>
       <c r="L38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.6">
@@ -2655,7 +2679,7 @@
         <v>37</v>
       </c>
       <c r="L39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6">
@@ -2674,10 +2698,10 @@
         <v>35</v>
       </c>
       <c r="G40" t="s">
+        <v>142</v>
+      </c>
+      <c r="H40" t="s">
         <v>143</v>
-      </c>
-      <c r="H40" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6">
@@ -2696,16 +2720,16 @@
         <v>41</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s">
+        <v>204</v>
+      </c>
+      <c r="M41" t="s">
         <v>205</v>
-      </c>
-      <c r="M41" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6">
@@ -2721,22 +2745,22 @@
         <v>Wed</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.6">
@@ -2752,16 +2776,16 @@
         <v>Fri</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.6">
@@ -2780,16 +2804,16 @@
         <v>38</v>
       </c>
       <c r="E44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.6">
@@ -2808,16 +2832,16 @@
         <v>42</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L45" t="s">
+        <v>210</v>
+      </c>
+      <c r="M45" t="s">
         <v>211</v>
-      </c>
-      <c r="M45" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15.6">
@@ -2839,7 +2863,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G46" s="9"/>
     </row>
@@ -2856,20 +2880,20 @@
         <v>Mon</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>4</v>
       </c>
       <c r="G47" s="18"/>
       <c r="L47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M47" t="s">
         <v>174</v>
-      </c>
-      <c r="M47" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15.6">
@@ -2894,15 +2918,15 @@
         <v>8</v>
       </c>
       <c r="L48" t="s">
+        <v>212</v>
+      </c>
+      <c r="M48" t="s">
         <v>213</v>
-      </c>
-      <c r="M48" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="L49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="14.4">
@@ -2914,7 +2938,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="L53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2934,9 +2958,11 @@
     <hyperlink ref="I11" r:id="rId10" xr:uid="{9DB554BE-F1E7-4A10-8857-6AD7EE61C4F9}"/>
     <hyperlink ref="I12" r:id="rId11" xr:uid="{A0BE5509-76CC-47EB-8F87-CE802986609C}"/>
     <hyperlink ref="I13" r:id="rId12" xr:uid="{17E1DBA7-1282-4B9C-AE93-3520A2CC1B70}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{B2838FD0-63F6-4E7A-BA3A-876EF84E7420}"/>
+    <hyperlink ref="I15" r:id="rId14" xr:uid="{284CEF5E-CA76-42E6-ABDD-B2562CA15DD5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="portrait" r:id="rId13"/>
-  <legacyDrawing r:id="rId14"/>
+  <pageSetup scale="85" orientation="portrait" r:id="rId15"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
--- a/courses/Reg/DailyRecord.xlsx
+++ b/courses/Reg/DailyRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbarreto\Documents\GitHub\homepage\courses\Reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72612D85-222D-4E7C-8447-13E7512799B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FE1549-D8F6-42DF-820B-CA5A57083D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,42 +36,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Humberto Barreto</author>
-  </authors>
-  <commentList>
-    <comment ref="H25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Humberto Barreto:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-VBA done later in Confidence Intervals</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="287">
   <si>
     <t>Grade</t>
   </si>
@@ -361,36 +327,18 @@
     <t>No handout</t>
   </si>
   <si>
-    <t>NONE</t>
-  </si>
-  <si>
     <t>Measurement Error Model</t>
   </si>
   <si>
     <t>Introduce measurement error, 3 SEs of sample average again</t>
   </si>
   <si>
-    <t>15.Measure &amp; 16 prep, n=100 SE</t>
-  </si>
-  <si>
-    <t>15.Measure.doc</t>
-  </si>
-  <si>
-    <t>Use 15.MeasurePreClass</t>
-  </si>
-  <si>
     <t>measurement error in reg context, SE of sample slope</t>
   </si>
   <si>
     <t>16.MeasureReg &amp; 17 prep, b1 sim</t>
   </si>
   <si>
-    <t>16.MeasureReg.doc</t>
-  </si>
-  <si>
-    <t>Use their prepped Excel file (I have one in Classes25 folder)</t>
-  </si>
-  <si>
     <t>Multivariate Regression SE of slope</t>
   </si>
   <si>
@@ -413,12 +361,6 @@
   </si>
   <si>
     <t>Use 18.CEM</t>
-  </si>
-  <si>
-    <t>Use their prepped Excel file</t>
-  </si>
-  <si>
-    <t>68% CI with n=5 and n=100</t>
   </si>
   <si>
     <t>23.CI</t>
@@ -493,36 +435,15 @@
     <t>Intro, Windows App, Stats Review</t>
   </si>
   <si>
-    <t>Use 16.MeasureRegPreClass</t>
-  </si>
-  <si>
-    <t>build univariate GM</t>
-  </si>
-  <si>
-    <t>19.Univariate.doc</t>
-  </si>
-  <si>
-    <t>from scratch</t>
-  </si>
-  <si>
     <t>21.RobustReg</t>
   </si>
   <si>
-    <t>Use 20.GMBI.xls</t>
-  </si>
-  <si>
     <t>20.GMReg</t>
   </si>
   <si>
-    <t>21.LMS and 22 all of it</t>
-  </si>
-  <si>
     <t>grade in class, est SE computed? Est SE biased? Omit X4 effect?</t>
   </si>
   <si>
-    <t>Use 21.LMSPreClass, put. bas in public, only import</t>
-  </si>
-  <si>
     <t>25.JointHypoTest</t>
   </si>
   <si>
@@ -539,12 +460,6 @@
   </si>
   <si>
     <t>Use 24.HypoTestPreClass</t>
-  </si>
-  <si>
-    <t>Use 23.UtilizingSEPreClass</t>
-  </si>
-  <si>
-    <t>Use 25.JointHypoTestPreClass again</t>
   </si>
   <si>
     <t>27.HetEffects</t>
@@ -718,19 +633,10 @@
     <t>Cuban Elvis</t>
   </si>
   <si>
-    <t>Japan visitor</t>
-  </si>
-  <si>
     <t>Guantanamera</t>
   </si>
   <si>
     <t>Ojala que llueva café</t>
-  </si>
-  <si>
-    <t>Night Fever</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=e6GB04zeDeQ</t>
   </si>
   <si>
     <t>Body Electric</t>
@@ -936,13 +842,172 @@
   </si>
   <si>
     <t>https://depauw-edu.zoom.us/rec/share/YgPD9M5qq2ZoYC1bbprhEdyy3yMi8x5V7X19fFkJlalCd04Ba-6DF1Tw5ZnxbBAg.l2hOVlM_9gV7FShe</t>
+  </si>
+  <si>
+    <t>Passcode: YeujE.2!</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/AU7eTe3HQqv1iAdWmsxCZB7fSwof20Q5IuZkWI5G1RanjhIBGq9VrEHyUO3YUg_v.k5oPE5UBY3BgeKtT</t>
+  </si>
+  <si>
+    <t>Passcode: .yFH*5md</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/sDDRC8AUYOc-kkzteg9ZGK-5LrR7m4HfYGg-yiGzDeS95MNfeucsqZQsQ2q7DL5O.YpS6cvuZUunJBFWM</t>
+  </si>
+  <si>
+    <t>NONE (Take a break)</t>
+  </si>
+  <si>
+    <t>15.Measurement Error</t>
+  </si>
+  <si>
+    <t>Night Fever video</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=e6GB04zeDeQ</t>
+  </si>
+  <si>
+    <t>Passcode: 3K5y!N+J</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/GZ3RC2GBUnESLea6xgPKb4ajz9iCR_LkY65C7i4pKkEh5_HZSmbrkkN3jDAxAH8.sAKs06uISDRGwqa0</t>
+  </si>
+  <si>
+    <t>Use 15.MeasureErrorPreClass</t>
+  </si>
+  <si>
+    <t>15.MeasureError.doc</t>
+  </si>
+  <si>
+    <t>16.MeasureErrorReg.doc</t>
+  </si>
+  <si>
+    <t>Use 16.MeasureErrorRegPreClass</t>
+  </si>
+  <si>
+    <t>Passcode: rFp58&amp;O6</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/0QFyjU17rgqnlj5vOEt17WY-MUKPq4s-RjiO1LflEFJPqIsVG0Q7UjRRUMXeDj6Q.Uks4lVawUOXYbB-a</t>
+  </si>
+  <si>
+    <t>zoom</t>
+  </si>
+  <si>
+    <t>exam</t>
+  </si>
+  <si>
+    <t>Use a student's file (or 17.PreClass), save as to public folder</t>
+  </si>
+  <si>
+    <t>Passcode: @kb9LBU1</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/_yzHNg6uuyMOfzGwk8b8XTh1xXfq58l7TvS1txQxSQaAn23KipO2avwZxggUBAps.KfYB3pSeNRY_GLxh</t>
+  </si>
+  <si>
+    <t>Passcode: 9Z&amp;YqBjI</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/v03uwOsjOYdyo1RApKPxG5iIlCdBLT4UDwOkFRIq-KHxmPsq13H8AwIxKz9SIikG.HA3AZsjLWRmzmZZg</t>
+  </si>
+  <si>
+    <t>19.GMUni.doc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">from scratch, but there is a 19.GMUniPreClass.xlsx </t>
+  </si>
+  <si>
+    <t>Passcode: !Zc=K=4M</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/SYknr1IBFGa0EqNMNIwvRdroEY3aIfp8gOkOUH8pJ-0CK_z73z3g0fqjXZrB1BaL.jduBwlEaCJFusQBn</t>
+  </si>
+  <si>
+    <t>build univariate, demo GM via sims</t>
+  </si>
+  <si>
+    <t>Use 20.GMRegPreClass.xls</t>
+  </si>
+  <si>
+    <t>Passcode: 8*gKp6uQ</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/pjmrMHQPyFkFnkcDZ7InshMJxXpa-DSiK4f_KSikl1ZkmX-WiDgPbRLEDtqrCsr5.u0POW2AwSDpyblmx</t>
+  </si>
+  <si>
+    <t>Use 21.LMSPreClass, put. bas in public, only import, VBA done in CI</t>
+  </si>
+  <si>
+    <t>Grade their Excel files in front of class, go fast</t>
+  </si>
+  <si>
+    <t>Passcode: cDX%rx1p</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/uxfne8g5W8Iz48l9w14vDzOOknTC_9UrMp2YGeC16WwmrqScIE1mwLzQ-d1nPz3V.WlxMe0_ginZ5YeQy</t>
+  </si>
+  <si>
+    <t>air media would not play it after I adjusted the volume</t>
+  </si>
+  <si>
+    <t>22 all of it</t>
+  </si>
+  <si>
+    <t>22 Workshop, No handout</t>
+  </si>
+  <si>
+    <t>ask one question</t>
+  </si>
+  <si>
+    <t>Passcode: @y%rjcQ3</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/swTXwX6tE5UKs7rGpDgQ_2RCgb-x8w_weNGtKShYCd4Gpn2A-8YqccG5wzqZ8LzY.YY2k84vkU11CX_Ex</t>
+  </si>
+  <si>
+    <t>Use 23.SEPreClass</t>
+  </si>
+  <si>
+    <t>Kodachrome</t>
+  </si>
+  <si>
+    <t>68% CI with n=5 and n=100, understand Est SE and t dist</t>
+  </si>
+  <si>
+    <t>Passcode: @Y4EXkLS</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/nILnRyItwbyejBoQMIHi2hAitX7Zsbpvbdb1Iw6RUA29W0b0DCoTrU5AY4uWPCoK.IDlCFfRuTn6EilL2</t>
+  </si>
+  <si>
+    <t>Passcode: WU6%xb5C</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/UrKtTqDha8DDW9TuykHsnUmi1P3CW40d9YH6lQSfh9wMf3-1i0Di6AFijplgnCcZ.tm4ajmcVZnCmCzDb</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/QxTeTPnl5XUrbYDk-noM8xTx4mlfG0GIY4nH2alZrAEpFcxG2lueW-iIpEHLxPkb.EoN1Fejzw4jC7vdu</t>
+  </si>
+  <si>
+    <t>Use saved 25.JointHypo.xlsx from last class, save as 26.WholeModelF</t>
+  </si>
+  <si>
+    <t>Passcode: KwtXV22.</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/uer43ydmisN8lTqJl-5jJetrIMm_OKDCI1LLH5mFLTxFw51M0sZgijCcaibcBf__.JKtOtJzShcJkxXPr</t>
+  </si>
+  <si>
+    <t>Passcode: 1b4@^yU9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <sz val="9"/>
       <name val="Geneva"/>
@@ -991,19 +1056,6 @@
       <sz val="11"/>
       <color indexed="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -1091,17 +1143,17 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1126,22 +1178,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1150,20 +1202,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1538,11 +1593,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr defaultRowHeight="11.4"/>
   <cols>
     <col min="3" max="3" width="8.625" customWidth="1"/>
@@ -1550,7 +1605,7 @@
     <col min="5" max="5" width="59" customWidth="1"/>
     <col min="6" max="6" width="25.875" customWidth="1"/>
     <col min="7" max="7" width="27.75" customWidth="1"/>
-    <col min="8" max="8" width="56.875" customWidth="1"/>
+    <col min="8" max="8" width="58.75" customWidth="1"/>
     <col min="9" max="9" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1563,7 +1618,7 @@
     </row>
     <row r="2" spans="1:18" ht="13.2">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1571,11 +1626,11 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="24" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16.2" thickBot="1">
@@ -1595,20 +1650,20 @@
         <v>12</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="J4" s="27"/>
+        <v>211</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="J4" s="28"/>
       <c r="L4" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.6">
@@ -1623,25 +1678,28 @@
         <v>Mon</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
         <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="G5" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="H5" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="J5" t="s">
-        <v>165</v>
+        <v>148</v>
+      </c>
+      <c r="L5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.6">
@@ -1663,22 +1721,22 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="G6" t="s">
         <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="J6" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L6" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="24">
@@ -1700,22 +1758,22 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="J7" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="L7" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.6">
@@ -1737,7 +1795,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="G8" t="s">
         <v>53</v>
@@ -1746,13 +1804,13 @@
         <v>54</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="J8" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="L8" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.6">
@@ -1783,19 +1841,19 @@
         <v>57</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="J9" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="L9" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="R9" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.6">
@@ -1814,7 +1872,7 @@
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
@@ -1823,19 +1881,19 @@
         <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="J10" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="L10" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.6">
@@ -1863,16 +1921,16 @@
         <v>64</v>
       </c>
       <c r="H11" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="J11" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="L11" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.6">
@@ -1891,25 +1949,25 @@
         <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="F12" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="G12" t="s">
         <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="J12" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="L12" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.6">
@@ -1928,7 +1986,7 @@
         <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -1940,13 +1998,13 @@
         <v>70</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="J13" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="L13" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.6">
@@ -1977,13 +2035,13 @@
         <v>74</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="J14" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="L14" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.6">
@@ -2011,16 +2069,16 @@
         <v>77</v>
       </c>
       <c r="H15" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="J15" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="L15" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.6">
@@ -2050,8 +2108,14 @@
       <c r="H16" t="s">
         <v>80</v>
       </c>
+      <c r="I16" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="J16" t="s">
+        <v>234</v>
+      </c>
       <c r="L16" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6">
@@ -2078,6 +2142,15 @@
       <c r="G17" t="s">
         <v>83</v>
       </c>
+      <c r="I17" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="J17" t="s">
+        <v>236</v>
+      </c>
+      <c r="L17" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="15.6">
       <c r="A18" s="2">
@@ -2095,14 +2168,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="G18" s="6"/>
       <c r="L18" t="s">
-        <v>180</v>
-      </c>
-      <c r="M18" t="s">
-        <v>181</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6">
@@ -2118,22 +2188,31 @@
         <v>Fri</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
         <v>85</v>
       </c>
-      <c r="E19" t="s">
-        <v>86</v>
-      </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>239</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>245</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>244</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="J19" t="s">
+        <v>242</v>
       </c>
       <c r="L19" t="s">
-        <v>176</v>
+        <v>240</v>
+      </c>
+      <c r="M19" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6">
@@ -2152,16 +2231,25 @@
         <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>92</v>
+        <v>246</v>
       </c>
       <c r="H20" t="s">
-        <v>116</v>
+        <v>247</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="J20" t="s">
+        <v>248</v>
+      </c>
+      <c r="L20" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6">
@@ -2177,22 +2265,28 @@
         <v>Wed</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>252</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="J21" t="s">
+        <v>253</v>
       </c>
       <c r="L21" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6">
@@ -2211,22 +2305,25 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="J22" t="s">
+        <v>255</v>
       </c>
       <c r="L22" t="s">
-        <v>184</v>
-      </c>
-      <c r="M22" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6">
@@ -2245,19 +2342,25 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>117</v>
+        <v>261</v>
       </c>
       <c r="F23" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="G23" t="s">
-        <v>118</v>
+        <v>257</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>258</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="J23" t="s">
+        <v>259</v>
       </c>
       <c r="L23" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6">
@@ -2276,16 +2379,19 @@
         <v>28</v>
       </c>
       <c r="F24" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="G24" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="H24" t="s">
-        <v>121</v>
-      </c>
-      <c r="L24" t="s">
-        <v>187</v>
+        <v>262</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="J24" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6">
@@ -2304,16 +2410,22 @@
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>123</v>
+        <v>270</v>
       </c>
       <c r="G25" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H25" t="s">
-        <v>125</v>
+        <v>265</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="J25" t="s">
+        <v>267</v>
       </c>
       <c r="L25" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6">
@@ -2332,16 +2444,25 @@
         <v>30</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>124</v>
+        <v>110</v>
+      </c>
+      <c r="F26" t="s">
+        <v>272</v>
       </c>
       <c r="G26" t="s">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
+        <v>266</v>
+      </c>
+      <c r="I26" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="J26" t="s">
+        <v>273</v>
       </c>
       <c r="L26" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6">
@@ -2360,19 +2481,25 @@
         <v>32</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="F27" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="G27" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H27" t="s">
-        <v>132</v>
+        <v>275</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="J27" t="s">
+        <v>278</v>
       </c>
       <c r="L27" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6">
@@ -2391,16 +2518,25 @@
         <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>116</v>
+      </c>
+      <c r="I28" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="J28" t="s">
+        <v>280</v>
+      </c>
+      <c r="L28" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6">
@@ -2430,9 +2566,6 @@
       <c r="D30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L30" t="s">
-        <v>191</v>
-      </c>
     </row>
     <row r="31" spans="1:13" ht="15.6">
       <c r="A31" s="2">
@@ -2447,12 +2580,6 @@
       <c r="D31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L31" t="s">
-        <v>192</v>
-      </c>
-      <c r="M31" t="s">
-        <v>193</v>
-      </c>
     </row>
     <row r="32" spans="1:13" ht="15.6">
       <c r="A32" s="2">
@@ -2470,19 +2597,22 @@
         <v>33</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F32" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="G32" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="H32" t="s">
-        <v>130</v>
-      </c>
-      <c r="L32" t="s">
-        <v>194</v>
+        <v>115</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="J32" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.6">
@@ -2501,19 +2631,28 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="F33" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="G33" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
-        <v>133</v>
+        <v>283</v>
+      </c>
+      <c r="I33" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="J33" t="s">
+        <v>286</v>
       </c>
       <c r="L33" t="s">
-        <v>195</v>
+        <v>184</v>
+      </c>
+      <c r="M33" s="24" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.6">
@@ -2532,19 +2671,16 @@
         <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="L34" t="s">
-        <v>196</v>
-      </c>
-      <c r="M34" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15.6">
@@ -2563,19 +2699,16 @@
         <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G35" t="s">
-        <v>135</v>
-      </c>
-      <c r="L35" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="M35" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15.6">
@@ -2591,13 +2724,16 @@
         <v>Wed</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E36" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F36" t="s">
-        <v>145</v>
+        <v>128</v>
+      </c>
+      <c r="L36" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="16.2" thickBot="1">
@@ -2622,13 +2758,10 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="L37" t="s">
-        <v>200</v>
-      </c>
-      <c r="M37" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.6">
@@ -2647,17 +2780,20 @@
         <v>10</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" t="s">
         <v>36</v>
       </c>
       <c r="L38" t="s">
-        <v>202</v>
+        <v>174</v>
+      </c>
+      <c r="M38" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.6">
@@ -2679,7 +2815,10 @@
         <v>37</v>
       </c>
       <c r="L39" t="s">
-        <v>203</v>
+        <v>175</v>
+      </c>
+      <c r="M39" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6">
@@ -2698,10 +2837,13 @@
         <v>35</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="H40" t="s">
-        <v>143</v>
+        <v>126</v>
+      </c>
+      <c r="L40" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6">
@@ -2720,16 +2862,16 @@
         <v>41</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="M41" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6">
@@ -2745,22 +2887,22 @@
         <v>Wed</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="L42" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.6">
@@ -2776,16 +2918,16 @@
         <v>Fri</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="L43" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.6">
@@ -2804,16 +2946,19 @@
         <v>38</v>
       </c>
       <c r="E44" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G44" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>148</v>
+        <v>131</v>
+      </c>
+      <c r="L44" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.6">
@@ -2832,16 +2977,13 @@
         <v>42</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L45" t="s">
-        <v>210</v>
-      </c>
-      <c r="M45" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15.6">
@@ -2863,9 +3005,12 @@
         <v>5</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G46" s="9"/>
+      <c r="L46" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="15.6">
       <c r="A47" s="2">
@@ -2880,21 +3025,15 @@
         <v>Mon</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>4</v>
       </c>
       <c r="G47" s="18"/>
-      <c r="L47" t="s">
-        <v>173</v>
-      </c>
-      <c r="M47" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="48" spans="1:13" ht="15.6">
       <c r="A48" s="2">
@@ -2918,27 +3057,46 @@
         <v>8</v>
       </c>
       <c r="L48" t="s">
-        <v>212</v>
-      </c>
-      <c r="M48" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="L49" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="14.4">
+        <v>187</v>
+      </c>
+      <c r="M49" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="14.4">
       <c r="A51" s="20"/>
       <c r="C51" s="21"/>
-    </row>
-    <row r="52" spans="1:12" ht="14.4">
+      <c r="L51" t="s">
+        <v>190</v>
+      </c>
+      <c r="M51" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="14.4">
       <c r="B52" s="21"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="L53" t="s">
-        <v>215</v>
+      <c r="M52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="L54" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="L55" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="L59" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2960,9 +3118,23 @@
     <hyperlink ref="I13" r:id="rId12" xr:uid="{17E1DBA7-1282-4B9C-AE93-3520A2CC1B70}"/>
     <hyperlink ref="I14" r:id="rId13" xr:uid="{B2838FD0-63F6-4E7A-BA3A-876EF84E7420}"/>
     <hyperlink ref="I15" r:id="rId14" xr:uid="{284CEF5E-CA76-42E6-ABDD-B2562CA15DD5}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{740748D9-3731-4D44-90E6-D444B3DFFCDA}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{66888497-A698-4D0D-A51C-3F6EF823B9DB}"/>
+    <hyperlink ref="I19" r:id="rId17" xr:uid="{4AC4DC58-D110-49BA-AE55-2D0EC7976090}"/>
+    <hyperlink ref="I20" r:id="rId18" xr:uid="{A4C4F584-67AC-4B2D-9137-C45F31F04441}"/>
+    <hyperlink ref="I21" r:id="rId19" xr:uid="{266AF027-98B3-4D9C-8AB8-C8B1B42BAD7B}"/>
+    <hyperlink ref="I22" r:id="rId20" xr:uid="{FEC1AA73-808D-4A29-9E5F-50B1A3E7721F}"/>
+    <hyperlink ref="I23" r:id="rId21" xr:uid="{8B44EAEB-E310-4371-8C4C-2F58A07E7C87}"/>
+    <hyperlink ref="I24" r:id="rId22" xr:uid="{3942BA65-4836-4C7A-95F8-6C4B19B38220}"/>
+    <hyperlink ref="I25" r:id="rId23" xr:uid="{EB0A94FC-1253-44E8-A838-2C52B3979496}"/>
+    <hyperlink ref="I26" r:id="rId24" xr:uid="{BFEB963A-7643-41BF-9C5D-4A5452BD9A9D}"/>
+    <hyperlink ref="I27" r:id="rId25" xr:uid="{F3195E4E-9BDD-4125-BBD6-A00170E588CA}"/>
+    <hyperlink ref="I28" r:id="rId26" xr:uid="{A7A55F02-5B29-4375-AB5F-BE0C0B59FFE1}"/>
+    <hyperlink ref="I32" r:id="rId27" xr:uid="{7BBB8307-26C1-4A6B-A11B-C046A9E889A3}"/>
+    <hyperlink ref="M33" r:id="rId28" xr:uid="{A99321CF-3833-4711-9272-617D4ADACDCC}"/>
+    <hyperlink ref="I33" r:id="rId29" xr:uid="{90B349C4-33E9-4C05-A37C-6D393BD1852A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="portrait" r:id="rId15"/>
-  <legacyDrawing r:id="rId16"/>
+  <pageSetup scale="85" orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>
--- a/courses/Reg/DailyRecord.xlsx
+++ b/courses/Reg/DailyRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbarreto\Documents\GitHub\homepage\courses\Reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FE1549-D8F6-42DF-820B-CA5A57083D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BA2E53-1B8A-445C-859E-973DA8C446F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="293">
   <si>
     <t>Grade</t>
   </si>
@@ -373,9 +373,6 @@
   </si>
   <si>
     <t>Do chisq, F and Exp &amp; Exp^2</t>
-  </si>
-  <si>
-    <t>28.27Het</t>
   </si>
   <si>
     <t>Exam Q&amp;A</t>
@@ -450,9 +447,6 @@
     <t>Do Whole Model F on ExpExp2 and SNAP in class</t>
   </si>
   <si>
-    <t>Questions in Word doc</t>
-  </si>
-  <si>
     <t>26.WholeModelF</t>
   </si>
   <si>
@@ -498,9 +492,6 @@
     <t>Study</t>
   </si>
   <si>
-    <t>Bring questions</t>
-  </si>
-  <si>
     <t>Orthoreg.xlsm</t>
   </si>
   <si>
@@ -528,11 +519,472 @@
     <t>24.Hypothesis Testing</t>
   </si>
   <si>
-    <t>25JointHypoTest</t>
+    <t>Handouts (has HW)</t>
+  </si>
+  <si>
+    <t>Binary Response DGP and LPM</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Reading for </t>
+      <t xml:space="preserve">Text: Barreto, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <rFont val="Geneva"/>
+      </rPr>
+      <t>Regression with Microdata and Microsoft Excel</t>
+    </r>
+  </si>
+  <si>
+    <t>dub.sh/regcourse</t>
+  </si>
+  <si>
+    <t>FINAL PAPER PRESENTATION Max 5 minute w/ slides</t>
+  </si>
+  <si>
+    <t>Zoom video link</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/ICNzqLZgGiAc_ag012Lyg9kh-OpC2vtVSRgFZV1GMbboLGXf9s6eWOat08c2zzSx.WK0Lk7pnjIGZE7QX?startTime=1769440479000</t>
+  </si>
+  <si>
+    <t>Passcode: E+a46@yb</t>
+  </si>
+  <si>
+    <t>Song</t>
+  </si>
+  <si>
+    <t>Pitbull Guantanamera</t>
+  </si>
+  <si>
+    <t>Irakere Marie Laveaux</t>
+  </si>
+  <si>
+    <t>Viene a pedir mi mano</t>
+  </si>
+  <si>
+    <t>Chan Chan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tGbRZ73NvlY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=o5cELP06Mik&amp;t=2s</t>
+  </si>
+  <si>
+    <t>Telephone Line</t>
+  </si>
+  <si>
+    <t>El Cuarto de Tula video</t>
+  </si>
+  <si>
+    <t>One tin soldier video</t>
+  </si>
+  <si>
+    <t>Let's Stay Together</t>
+  </si>
+  <si>
+    <t>Mi Tierra</t>
+  </si>
+  <si>
+    <t>This Land is Your Land</t>
+  </si>
+  <si>
+    <t>Cuban Elvis</t>
+  </si>
+  <si>
+    <t>Guantanamera</t>
+  </si>
+  <si>
+    <t>Ojala que llueva café</t>
+  </si>
+  <si>
+    <t>Body Electric</t>
+  </si>
+  <si>
+    <t>Picabo Street skiing video</t>
+  </si>
+  <si>
+    <t>rocky raccoon</t>
+  </si>
+  <si>
+    <t>Fire on High</t>
+  </si>
+  <si>
+    <t>City of New Orleans</t>
+  </si>
+  <si>
+    <t>Heart of Gold</t>
+  </si>
+  <si>
+    <t>Band of Gold</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jhuDgUnqXUY&amp;t=16s</t>
+  </si>
+  <si>
+    <t>Lido Shuffle</t>
+  </si>
+  <si>
+    <t>Goodbye Earl</t>
+  </si>
+  <si>
+    <t>Marvin</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FrkEDe6Ljqs</t>
+  </si>
+  <si>
+    <t>Black or White</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=F2AitTPI5U0</t>
+  </si>
+  <si>
+    <t>Ode to Joy</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=kbJcQYVtZMo&amp;t=2s</t>
+  </si>
+  <si>
+    <t>Oye Como Va</t>
+  </si>
+  <si>
+    <t>Light My Fire</t>
+  </si>
+  <si>
+    <t>Get Ready</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=A3Ix4hKSnxQ</t>
+  </si>
+  <si>
+    <t>Everyday People</t>
+  </si>
+  <si>
+    <t>Fast Car Grammys</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pLfH9HSUyf4</t>
+  </si>
+  <si>
+    <t>Texas Hold Em</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ycwtqqhV6UE</t>
+  </si>
+  <si>
+    <t>Shaft</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZVj8FgMMAK8&amp;t=96s</t>
+  </si>
+  <si>
+    <t>Long and Winding Road</t>
+  </si>
+  <si>
+    <t>Southern Cross</t>
+  </si>
+  <si>
+    <t>1.JourneyBegins</t>
+  </si>
+  <si>
+    <t>2.CMF &amp; up to p.4 of 3.Mechanics</t>
+  </si>
+  <si>
+    <t>2.CPSIncEducPreClass,xlsx</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/ZmQPaxZLWJcUqKWyTjAmZrkhPtanB96Dz7X6hXwETAeUprHzO7fcp052eLiNBARs.W6ahgehJLXD39ai1?startTime=1769613455000</t>
+  </si>
+  <si>
+    <t>Passcode: 7y$ae?C$</t>
+  </si>
+  <si>
+    <t>3.Mechanics &amp; up to p. 4.Interpret</t>
+  </si>
+  <si>
+    <t>Passcode: d&amp;9eKD5K</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/7Ye7b5N7JoPTF0ltSlnbW_566rJDV26uMjVKKgAHzBjINVD3hnynEsugkM4s18UK.7jq4XKs7ucDlkNZ0</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/dFkNbZT_V0gQz2yHDSYiOdTXOo4n-8tEvALIBUhr91LFHXZeluUZZdgAgUXZYTl5.PFaUCOYz3YJfnTT6?startTime=1770045404000</t>
+  </si>
+  <si>
+    <t>Passcode: q4E.A&amp;x+</t>
+  </si>
+  <si>
+    <t>4.Interpret, 4.Heights.xlsx questions</t>
+  </si>
+  <si>
+    <t>Passcode: u#5A3a0d</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/UNxi8SSaPQs-t2m2v_77yf8malSdp7W_gb95AYMGXwqgazgJA1S2Nqu2YYG3RXPh.5lct_YlgfzJzuzsr</t>
+  </si>
+  <si>
+    <t>1.CPSIncEducPreClass.xlsx</t>
+  </si>
+  <si>
+    <t>Every day has student and teacher Word doc</t>
+  </si>
+  <si>
+    <t>Class Prep Notes</t>
+  </si>
+  <si>
+    <t>Use a student's file, save as to public folder as 3.Mechanics.xlsx
+3.minSSRPreClass in folder just to see what to do</t>
+  </si>
+  <si>
+    <t>Use Google sheets, multreg and IncEducDrive</t>
+  </si>
+  <si>
+    <t>Fake X1, X2, Y data and fake IncWAGE = f(EducYears, Drive)</t>
+  </si>
+  <si>
+    <t>Passcode: 5+7sAi^8</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/5y24hfnP5N07-CNif4tm_846v_OrMwZqJaiGvppeFQIvUfLgtu_PJtLERKmDrdqN.TWlB_lwqUZtZfaCM</t>
+  </si>
+  <si>
+    <t>Passcode: 5v5rwF+H</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/ljCjP20z71Be4EpuJsm8Z9oC1T6f3WFxT124rXH_-cC_yvMNrz6ZSLAf75-YvXGb.EhOaidxzb3Z3lVoQ</t>
+  </si>
+  <si>
+    <t>8.Experience</t>
+  </si>
+  <si>
+    <t>PV theory is HW, focus on linear &amp; LN reg</t>
+  </si>
+  <si>
+    <t>8.ExperiencePreClass.xlsx, play Angrist in class, CMF, interpret Exp</t>
+  </si>
+  <si>
+    <t>Passcode: $C9TsL6V</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/8Ma03tb3qOC9X03KZ17FYqKAz42Jq1JklNBBzrMbhC7IZA-CA5irvVA6kClhJBkc.L4L-5dPo2Fzoaj0C</t>
+  </si>
+  <si>
+    <t>La Bamba</t>
+  </si>
+  <si>
+    <t>Discuss OVB, Add Exp and Exp^2</t>
+  </si>
+  <si>
+    <t>Discuss M and F, leave race/ethnicity for HW</t>
+  </si>
+  <si>
+    <t>Passcode: D0WUc@y#</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/XKeJyvUQqDwX_QOhT5GXLN3-kxlo8bg8kovnU5RiGcXok5aNCuZdj8RloVGeBH66.beRU6aLw7nUkbqTe</t>
+  </si>
+  <si>
+    <t>Passcode: 4G01d%Hz</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/lhHiHPHjmcnsDk4e1ASO8Ixsl8TI6dr2aroAu9UqHX4RaOIon1N9dfHp7597Q7VI.k11-6KZaV0KX79Om</t>
+  </si>
+  <si>
+    <t>Blank file, completed version 10.PollingPostClass.xls</t>
+  </si>
+  <si>
+    <t>Passcode: CY6ZNa=W</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/YgPD9M5qq2ZoYC1bbprhEdyy3yMi8x5V7X19fFkJlalCd04Ba-6DF1Tw5ZnxbBAg.l2hOVlM_9gV7FShe</t>
+  </si>
+  <si>
+    <t>Passcode: YeujE.2!</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/AU7eTe3HQqv1iAdWmsxCZB7fSwof20Q5IuZkWI5G1RanjhIBGq9VrEHyUO3YUg_v.k5oPE5UBY3BgeKtT</t>
+  </si>
+  <si>
+    <t>Passcode: .yFH*5md</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/sDDRC8AUYOc-kkzteg9ZGK-5LrR7m4HfYGg-yiGzDeS95MNfeucsqZQsQ2q7DL5O.YpS6cvuZUunJBFWM</t>
+  </si>
+  <si>
+    <t>NONE (Take a break)</t>
+  </si>
+  <si>
+    <t>15.Measurement Error</t>
+  </si>
+  <si>
+    <t>Night Fever video</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=e6GB04zeDeQ</t>
+  </si>
+  <si>
+    <t>Passcode: 3K5y!N+J</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/GZ3RC2GBUnESLea6xgPKb4ajz9iCR_LkY65C7i4pKkEh5_HZSmbrkkN3jDAxAH8.sAKs06uISDRGwqa0</t>
+  </si>
+  <si>
+    <t>Use 15.MeasureErrorPreClass</t>
+  </si>
+  <si>
+    <t>15.MeasureError.doc</t>
+  </si>
+  <si>
+    <t>16.MeasureErrorReg.doc</t>
+  </si>
+  <si>
+    <t>Use 16.MeasureErrorRegPreClass</t>
+  </si>
+  <si>
+    <t>Passcode: rFp58&amp;O6</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/0QFyjU17rgqnlj5vOEt17WY-MUKPq4s-RjiO1LflEFJPqIsVG0Q7UjRRUMXeDj6Q.Uks4lVawUOXYbB-a</t>
+  </si>
+  <si>
+    <t>zoom</t>
+  </si>
+  <si>
+    <t>exam</t>
+  </si>
+  <si>
+    <t>Use a student's file (or 17.PreClass), save as to public folder</t>
+  </si>
+  <si>
+    <t>Passcode: @kb9LBU1</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/_yzHNg6uuyMOfzGwk8b8XTh1xXfq58l7TvS1txQxSQaAn23KipO2avwZxggUBAps.KfYB3pSeNRY_GLxh</t>
+  </si>
+  <si>
+    <t>Passcode: 9Z&amp;YqBjI</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/v03uwOsjOYdyo1RApKPxG5iIlCdBLT4UDwOkFRIq-KHxmPsq13H8AwIxKz9SIikG.HA3AZsjLWRmzmZZg</t>
+  </si>
+  <si>
+    <t>19.GMUni.doc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">from scratch, but there is a 19.GMUniPreClass.xlsx </t>
+  </si>
+  <si>
+    <t>Passcode: !Zc=K=4M</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/SYknr1IBFGa0EqNMNIwvRdroEY3aIfp8gOkOUH8pJ-0CK_z73z3g0fqjXZrB1BaL.jduBwlEaCJFusQBn</t>
+  </si>
+  <si>
+    <t>build univariate, demo GM via sims</t>
+  </si>
+  <si>
+    <t>Use 20.GMRegPreClass.xls</t>
+  </si>
+  <si>
+    <t>Passcode: 8*gKp6uQ</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/pjmrMHQPyFkFnkcDZ7InshMJxXpa-DSiK4f_KSikl1ZkmX-WiDgPbRLEDtqrCsr5.u0POW2AwSDpyblmx</t>
+  </si>
+  <si>
+    <t>Use 21.LMSPreClass, put. bas in public, only import, VBA done in CI</t>
+  </si>
+  <si>
+    <t>Grade their Excel files in front of class, go fast</t>
+  </si>
+  <si>
+    <t>Passcode: cDX%rx1p</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/uxfne8g5W8Iz48l9w14vDzOOknTC_9UrMp2YGeC16WwmrqScIE1mwLzQ-d1nPz3V.WlxMe0_ginZ5YeQy</t>
+  </si>
+  <si>
+    <t>air media would not play it after I adjusted the volume</t>
+  </si>
+  <si>
+    <t>22 all of it</t>
+  </si>
+  <si>
+    <t>22 Workshop, No handout</t>
+  </si>
+  <si>
+    <t>Passcode: @y%rjcQ3</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/swTXwX6tE5UKs7rGpDgQ_2RCgb-x8w_weNGtKShYCd4Gpn2A-8YqccG5wzqZ8LzY.YY2k84vkU11CX_Ex</t>
+  </si>
+  <si>
+    <t>Use 23.SEPreClass</t>
+  </si>
+  <si>
+    <t>Kodachrome</t>
+  </si>
+  <si>
+    <t>68% CI with n=5 and n=100, understand Est SE and t dist</t>
+  </si>
+  <si>
+    <t>Passcode: @Y4EXkLS</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/nILnRyItwbyejBoQMIHi2hAitX7Zsbpvbdb1Iw6RUA29W0b0DCoTrU5AY4uWPCoK.IDlCFfRuTn6EilL2</t>
+  </si>
+  <si>
+    <t>Passcode: WU6%xb5C</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/UrKtTqDha8DDW9TuykHsnUmi1P3CW40d9YH6lQSfh9wMf3-1i0Di6AFijplgnCcZ.tm4ajmcVZnCmCzDb</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/QxTeTPnl5XUrbYDk-noM8xTx4mlfG0GIY4nH2alZrAEpFcxG2lueW-iIpEHLxPkb.EoN1Fejzw4jC7vdu</t>
+  </si>
+  <si>
+    <t>Passcode: KwtXV22.</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/uer43ydmisN8lTqJl-5jJetrIMm_OKDCI1LLH5mFLTxFw51M0sZgijCcaibcBf__.JKtOtJzShcJkxXPr</t>
+  </si>
+  <si>
+    <t>Passcode: 1b4@^yU9</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/JMMF_lYAvJrFUlC_q1-DTJEvqiUfaR_KuhPgb_7-_Ot3s8-qK1FJcoXvvdPy81-b.Ha-qjzuLsOqFwWO1</t>
+  </si>
+  <si>
+    <t>Passcode: r%k2Fr!*</t>
+  </si>
+  <si>
+    <t>Il Paradisi</t>
+  </si>
+  <si>
+    <t>Use 27.HetPreClass</t>
+  </si>
+  <si>
+    <t>Use saved 27.Het.xlsx from last class, save as 28.GLS.xlsx</t>
+  </si>
+  <si>
+    <t>Use saved 25.JointHypo.xlsx from last class, save as 26.WholeModelF.xlsx</t>
+  </si>
+  <si>
+    <t>build rival slope estimators, demo GM via sims</t>
+  </si>
+  <si>
+    <t>Solver woes and LMS v OLS with iid v dirty data</t>
+  </si>
+  <si>
+    <t>ask AI one question about CI</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To Do for </t>
     </r>
     <r>
       <rPr>
@@ -554,453 +1006,19 @@
     </r>
   </si>
   <si>
-    <t>Handouts (has HW)</t>
-  </si>
-  <si>
-    <t>Binary Response DGP and LPM</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Text: Barreto, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <rFont val="Geneva"/>
-      </rPr>
-      <t>Regression with Microdata and Microsoft Excel</t>
-    </r>
-  </si>
-  <si>
-    <t>dub.sh/regcourse</t>
-  </si>
-  <si>
-    <t>FINAL PAPER PRESENTATION Max 5 minute w/ slides</t>
-  </si>
-  <si>
-    <t>Zoom video link</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/ICNzqLZgGiAc_ag012Lyg9kh-OpC2vtVSRgFZV1GMbboLGXf9s6eWOat08c2zzSx.WK0Lk7pnjIGZE7QX?startTime=1769440479000</t>
-  </si>
-  <si>
-    <t>Passcode: E+a46@yb</t>
-  </si>
-  <si>
-    <t>Song</t>
-  </si>
-  <si>
-    <t>Pitbull Guantanamera</t>
-  </si>
-  <si>
-    <t>Irakere Marie Laveaux</t>
-  </si>
-  <si>
-    <t>Viene a pedir mi mano</t>
-  </si>
-  <si>
-    <t>Chan Chan</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=tGbRZ73NvlY</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=o5cELP06Mik&amp;t=2s</t>
-  </si>
-  <si>
-    <t>Telephone Line</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=XKElk9zTB04</t>
-  </si>
-  <si>
-    <t>El Cuarto de Tula video</t>
-  </si>
-  <si>
-    <t>One tin soldier video</t>
-  </si>
-  <si>
-    <t>Let's Stay Together</t>
-  </si>
-  <si>
-    <t>Mi Tierra</t>
-  </si>
-  <si>
-    <t>This Land is Your Land</t>
-  </si>
-  <si>
-    <t>Cuban Elvis</t>
-  </si>
-  <si>
-    <t>Guantanamera</t>
-  </si>
-  <si>
-    <t>Ojala que llueva café</t>
-  </si>
-  <si>
-    <t>Body Electric</t>
-  </si>
-  <si>
-    <t>Picabo Street skiing video</t>
-  </si>
-  <si>
-    <t>rocky raccoon</t>
-  </si>
-  <si>
-    <t>Fire on High</t>
-  </si>
-  <si>
-    <t>City of New Orleans</t>
-  </si>
-  <si>
-    <t>Heart of Gold</t>
-  </si>
-  <si>
-    <t>Band of Gold</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=jhuDgUnqXUY&amp;t=16s</t>
-  </si>
-  <si>
-    <t>Lido Shuffle</t>
-  </si>
-  <si>
-    <t>Goodbye Earl</t>
-  </si>
-  <si>
-    <t>Marvin</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=FrkEDe6Ljqs</t>
-  </si>
-  <si>
-    <t>Black or White</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=F2AitTPI5U0</t>
-  </si>
-  <si>
-    <t>Ode to Joy</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=kbJcQYVtZMo&amp;t=2s</t>
-  </si>
-  <si>
-    <t>Oye Como Va</t>
-  </si>
-  <si>
-    <t>Light My Fire</t>
-  </si>
-  <si>
-    <t>Get Ready</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=A3Ix4hKSnxQ</t>
-  </si>
-  <si>
-    <t>Edmund Fitzgerald</t>
-  </si>
-  <si>
-    <t>Everyday People</t>
-  </si>
-  <si>
-    <t>Fast Car Grammys</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=pLfH9HSUyf4</t>
-  </si>
-  <si>
-    <t>Texas Hold Em</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ycwtqqhV6UE</t>
-  </si>
-  <si>
-    <t>Shaft</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ZVj8FgMMAK8&amp;t=96s</t>
-  </si>
-  <si>
-    <t>Long and Winding Road</t>
-  </si>
-  <si>
-    <t>Southern Cross</t>
-  </si>
-  <si>
-    <t>1.JourneyBegins</t>
-  </si>
-  <si>
-    <t>2.CMF &amp; up to p.4 of 3.Mechanics</t>
-  </si>
-  <si>
-    <t>2.CPSIncEducPreClass,xlsx</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/ZmQPaxZLWJcUqKWyTjAmZrkhPtanB96Dz7X6hXwETAeUprHzO7fcp052eLiNBARs.W6ahgehJLXD39ai1?startTime=1769613455000</t>
-  </si>
-  <si>
-    <t>Passcode: 7y$ae?C$</t>
-  </si>
-  <si>
-    <t>3.Mechanics &amp; up to p. 4.Interpret</t>
-  </si>
-  <si>
-    <t>Passcode: d&amp;9eKD5K</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/7Ye7b5N7JoPTF0ltSlnbW_566rJDV26uMjVKKgAHzBjINVD3hnynEsugkM4s18UK.7jq4XKs7ucDlkNZ0</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/dFkNbZT_V0gQz2yHDSYiOdTXOo4n-8tEvALIBUhr91LFHXZeluUZZdgAgUXZYTl5.PFaUCOYz3YJfnTT6?startTime=1770045404000</t>
-  </si>
-  <si>
-    <t>Passcode: q4E.A&amp;x+</t>
-  </si>
-  <si>
-    <t>4.Interpret, 4.Heights.xlsx questions</t>
-  </si>
-  <si>
-    <t>Passcode: u#5A3a0d</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/UNxi8SSaPQs-t2m2v_77yf8malSdp7W_gb95AYMGXwqgazgJA1S2Nqu2YYG3RXPh.5lct_YlgfzJzuzsr</t>
-  </si>
-  <si>
-    <t>1.CPSIncEducPreClass.xlsx</t>
-  </si>
-  <si>
-    <t>Every day has student and teacher Word doc</t>
-  </si>
-  <si>
-    <t>Class Prep Notes</t>
-  </si>
-  <si>
-    <t>Use a student's file, save as to public folder as 3.Mechanics.xlsx
-3.minSSRPreClass in folder just to see what to do</t>
-  </si>
-  <si>
-    <t>Use Google sheets, multreg and IncEducDrive</t>
-  </si>
-  <si>
-    <t>Fake X1, X2, Y data and fake IncWAGE = f(EducYears, Drive)</t>
-  </si>
-  <si>
-    <t>Passcode: 5+7sAi^8</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/5y24hfnP5N07-CNif4tm_846v_OrMwZqJaiGvppeFQIvUfLgtu_PJtLERKmDrdqN.TWlB_lwqUZtZfaCM</t>
-  </si>
-  <si>
-    <t>Passcode: 5v5rwF+H</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/ljCjP20z71Be4EpuJsm8Z9oC1T6f3WFxT124rXH_-cC_yvMNrz6ZSLAf75-YvXGb.EhOaidxzb3Z3lVoQ</t>
-  </si>
-  <si>
-    <t>8.Experience</t>
-  </si>
-  <si>
-    <t>PV theory is HW, focus on linear &amp; LN reg</t>
-  </si>
-  <si>
-    <t>8.ExperiencePreClass.xlsx, play Angrist in class, CMF, interpret Exp</t>
-  </si>
-  <si>
-    <t>Passcode: $C9TsL6V</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/8Ma03tb3qOC9X03KZ17FYqKAz42Jq1JklNBBzrMbhC7IZA-CA5irvVA6kClhJBkc.L4L-5dPo2Fzoaj0C</t>
-  </si>
-  <si>
-    <t>La Bamba</t>
-  </si>
-  <si>
-    <t>Discuss OVB, Add Exp and Exp^2</t>
-  </si>
-  <si>
-    <t>Discuss M and F, leave race/ethnicity for HW</t>
-  </si>
-  <si>
-    <t>Passcode: D0WUc@y#</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/XKeJyvUQqDwX_QOhT5GXLN3-kxlo8bg8kovnU5RiGcXok5aNCuZdj8RloVGeBH66.beRU6aLw7nUkbqTe</t>
-  </si>
-  <si>
-    <t>Passcode: 4G01d%Hz</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/lhHiHPHjmcnsDk4e1ASO8Ixsl8TI6dr2aroAu9UqHX4RaOIon1N9dfHp7597Q7VI.k11-6KZaV0KX79Om</t>
-  </si>
-  <si>
-    <t>Blank file, completed version 10.PollingPostClass.xls</t>
-  </si>
-  <si>
-    <t>Passcode: CY6ZNa=W</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/YgPD9M5qq2ZoYC1bbprhEdyy3yMi8x5V7X19fFkJlalCd04Ba-6DF1Tw5ZnxbBAg.l2hOVlM_9gV7FShe</t>
-  </si>
-  <si>
-    <t>Passcode: YeujE.2!</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/AU7eTe3HQqv1iAdWmsxCZB7fSwof20Q5IuZkWI5G1RanjhIBGq9VrEHyUO3YUg_v.k5oPE5UBY3BgeKtT</t>
-  </si>
-  <si>
-    <t>Passcode: .yFH*5md</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/sDDRC8AUYOc-kkzteg9ZGK-5LrR7m4HfYGg-yiGzDeS95MNfeucsqZQsQ2q7DL5O.YpS6cvuZUunJBFWM</t>
-  </si>
-  <si>
-    <t>NONE (Take a break)</t>
-  </si>
-  <si>
-    <t>15.Measurement Error</t>
-  </si>
-  <si>
-    <t>Night Fever video</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=e6GB04zeDeQ</t>
-  </si>
-  <si>
-    <t>Passcode: 3K5y!N+J</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/GZ3RC2GBUnESLea6xgPKb4ajz9iCR_LkY65C7i4pKkEh5_HZSmbrkkN3jDAxAH8.sAKs06uISDRGwqa0</t>
-  </si>
-  <si>
-    <t>Use 15.MeasureErrorPreClass</t>
-  </si>
-  <si>
-    <t>15.MeasureError.doc</t>
-  </si>
-  <si>
-    <t>16.MeasureErrorReg.doc</t>
-  </si>
-  <si>
-    <t>Use 16.MeasureErrorRegPreClass</t>
-  </si>
-  <si>
-    <t>Passcode: rFp58&amp;O6</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/0QFyjU17rgqnlj5vOEt17WY-MUKPq4s-RjiO1LflEFJPqIsVG0Q7UjRRUMXeDj6Q.Uks4lVawUOXYbB-a</t>
-  </si>
-  <si>
-    <t>zoom</t>
-  </si>
-  <si>
-    <t>exam</t>
-  </si>
-  <si>
-    <t>Use a student's file (or 17.PreClass), save as to public folder</t>
-  </si>
-  <si>
-    <t>Passcode: @kb9LBU1</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/_yzHNg6uuyMOfzGwk8b8XTh1xXfq58l7TvS1txQxSQaAn23KipO2avwZxggUBAps.KfYB3pSeNRY_GLxh</t>
-  </si>
-  <si>
-    <t>Passcode: 9Z&amp;YqBjI</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/v03uwOsjOYdyo1RApKPxG5iIlCdBLT4UDwOkFRIq-KHxmPsq13H8AwIxKz9SIikG.HA3AZsjLWRmzmZZg</t>
-  </si>
-  <si>
-    <t>19.GMUni.doc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">from scratch, but there is a 19.GMUniPreClass.xlsx </t>
-  </si>
-  <si>
-    <t>Passcode: !Zc=K=4M</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/SYknr1IBFGa0EqNMNIwvRdroEY3aIfp8gOkOUH8pJ-0CK_z73z3g0fqjXZrB1BaL.jduBwlEaCJFusQBn</t>
-  </si>
-  <si>
-    <t>build univariate, demo GM via sims</t>
-  </si>
-  <si>
-    <t>Use 20.GMRegPreClass.xls</t>
-  </si>
-  <si>
-    <t>Passcode: 8*gKp6uQ</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/pjmrMHQPyFkFnkcDZ7InshMJxXpa-DSiK4f_KSikl1ZkmX-WiDgPbRLEDtqrCsr5.u0POW2AwSDpyblmx</t>
-  </si>
-  <si>
-    <t>Use 21.LMSPreClass, put. bas in public, only import, VBA done in CI</t>
-  </si>
-  <si>
-    <t>Grade their Excel files in front of class, go fast</t>
-  </si>
-  <si>
-    <t>Passcode: cDX%rx1p</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/uxfne8g5W8Iz48l9w14vDzOOknTC_9UrMp2YGeC16WwmrqScIE1mwLzQ-d1nPz3V.WlxMe0_ginZ5YeQy</t>
-  </si>
-  <si>
-    <t>air media would not play it after I adjusted the volume</t>
-  </si>
-  <si>
-    <t>22 all of it</t>
-  </si>
-  <si>
-    <t>22 Workshop, No handout</t>
-  </si>
-  <si>
-    <t>ask one question</t>
-  </si>
-  <si>
-    <t>Passcode: @y%rjcQ3</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/swTXwX6tE5UKs7rGpDgQ_2RCgb-x8w_weNGtKShYCd4Gpn2A-8YqccG5wzqZ8LzY.YY2k84vkU11CX_Ex</t>
-  </si>
-  <si>
-    <t>Use 23.SEPreClass</t>
-  </si>
-  <si>
-    <t>Kodachrome</t>
-  </si>
-  <si>
-    <t>68% CI with n=5 and n=100, understand Est SE and t dist</t>
-  </si>
-  <si>
-    <t>Passcode: @Y4EXkLS</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/nILnRyItwbyejBoQMIHi2hAitX7Zsbpvbdb1Iw6RUA29W0b0DCoTrU5AY4uWPCoK.IDlCFfRuTn6EilL2</t>
-  </si>
-  <si>
-    <t>Passcode: WU6%xb5C</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/UrKtTqDha8DDW9TuykHsnUmi1P3CW40d9YH6lQSfh9wMf3-1i0Di6AFijplgnCcZ.tm4ajmcVZnCmCzDb</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/QxTeTPnl5XUrbYDk-noM8xTx4mlfG0GIY4nH2alZrAEpFcxG2lueW-iIpEHLxPkb.EoN1Fejzw4jC7vdu</t>
-  </si>
-  <si>
-    <t>Use saved 25.JointHypo.xlsx from last class, save as 26.WholeModelF</t>
-  </si>
-  <si>
-    <t>Passcode: KwtXV22.</t>
-  </si>
-  <si>
-    <t>https://depauw-edu.zoom.us/rec/share/uer43ydmisN8lTqJl-5jJetrIMm_OKDCI1LLH5mFLTxFw51M0sZgijCcaibcBf__.JKtOtJzShcJkxXPr</t>
-  </si>
-  <si>
-    <t>Passcode: 1b4@^yU9</t>
+    <t>25.JointHypoTestIntro</t>
+  </si>
+  <si>
+    <t>27.Het &amp; Robust SE</t>
+  </si>
+  <si>
+    <t>28.HetGLS &amp; Bring 2 questions</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/9-_B05Wfg5iICKT0ZxFWSAM6P2E4N0Ec1AN0VGoQ4nMe7kMZwVIUdty3E6UyZTi6.ftV2Usj6l-NuZvut</t>
+  </si>
+  <si>
+    <t>Passcode: 0F?D%&amp;ZK</t>
   </si>
 </sst>
 </file>
@@ -1597,13 +1615,13 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="11.4"/>
   <cols>
     <col min="3" max="3" width="8.625" customWidth="1"/>
     <col min="4" max="4" width="55.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="59" customWidth="1"/>
-    <col min="6" max="6" width="25.875" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="27.75" customWidth="1"/>
     <col min="8" max="8" width="58.75" customWidth="1"/>
     <col min="9" max="9" width="11.75" customWidth="1"/>
@@ -1618,7 +1636,7 @@
     </row>
     <row r="2" spans="1:18" ht="13.2">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1626,11 +1644,11 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="24" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16.2" thickBot="1">
@@ -1650,20 +1668,20 @@
         <v>12</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>140</v>
+        <v>287</v>
       </c>
       <c r="G4" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="I4" s="28" t="s">
         <v>141</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>146</v>
       </c>
       <c r="J4" s="28"/>
       <c r="L4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.6">
@@ -1678,28 +1696,28 @@
         <v>Mon</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="J5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L5" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.6">
@@ -1721,22 +1739,22 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="G6" t="s">
         <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="24">
@@ -1758,22 +1776,22 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G7" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="L7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.6">
@@ -1795,7 +1813,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G8" t="s">
         <v>53</v>
@@ -1804,13 +1822,13 @@
         <v>54</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="J8" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.6">
@@ -1841,19 +1859,19 @@
         <v>57</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="L9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="R9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.6">
@@ -1872,7 +1890,7 @@
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
@@ -1881,19 +1899,19 @@
         <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J10" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="L10" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.6">
@@ -1921,16 +1939,16 @@
         <v>64</v>
       </c>
       <c r="H11" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="J11" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="L11" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.6">
@@ -1949,25 +1967,25 @@
         <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G12" t="s">
         <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="J12" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.6">
@@ -1986,7 +2004,7 @@
         <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -1998,13 +2016,13 @@
         <v>70</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="J13" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="L13" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.6">
@@ -2035,13 +2053,13 @@
         <v>74</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="J14" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="L14" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.6">
@@ -2069,16 +2087,16 @@
         <v>77</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="J15" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L15" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.6">
@@ -2109,13 +2127,13 @@
         <v>80</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="J16" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L16" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6">
@@ -2143,13 +2161,13 @@
         <v>83</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="J17" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L17" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6">
@@ -2168,11 +2186,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G18" s="6"/>
       <c r="L18" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6">
@@ -2194,25 +2212,25 @@
         <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G19" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="J19" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="L19" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="M19" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6">
@@ -2237,19 +2255,19 @@
         <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="H20" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="J20" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L20" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6">
@@ -2277,16 +2295,16 @@
         <v>91</v>
       </c>
       <c r="H21" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="J21" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L21" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6">
@@ -2317,13 +2335,13 @@
         <v>95</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="J22" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6">
@@ -2342,25 +2360,25 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G23" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="H23" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J23" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6">
@@ -2378,20 +2396,23 @@
       <c r="D24" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E24" t="s">
+        <v>284</v>
+      </c>
       <c r="F24" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H24" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="J24" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6">
@@ -2409,23 +2430,26 @@
       <c r="D25" s="6" t="s">
         <v>29</v>
       </c>
+      <c r="E25" t="s">
+        <v>285</v>
+      </c>
       <c r="F25" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H25" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J25" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="L25" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6">
@@ -2444,25 +2468,28 @@
         <v>30</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F26" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="G26" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H26" t="s">
+        <v>259</v>
+      </c>
+      <c r="I26" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="I26" s="24" t="s">
-        <v>274</v>
-      </c>
       <c r="J26" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s">
-        <v>176</v>
+        <v>170</v>
+      </c>
+      <c r="M26" s="24" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6">
@@ -2481,25 +2508,25 @@
         <v>32</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
         <v>96</v>
       </c>
       <c r="H27" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="J27" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6">
@@ -2521,23 +2548,24 @@
         <v>97</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G28" t="s">
         <v>98</v>
       </c>
       <c r="H28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="J28" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s">
-        <v>156</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="M28" s="24"/>
     </row>
     <row r="29" spans="1:13" ht="15.6">
       <c r="A29" s="2">
@@ -2600,19 +2628,19 @@
         <v>99</v>
       </c>
       <c r="F32" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>288</v>
       </c>
       <c r="H32" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="J32" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.6">
@@ -2631,28 +2659,28 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" t="s">
         <v>112</v>
       </c>
-      <c r="F33" t="s">
-        <v>113</v>
-      </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H33" t="s">
         <v>283</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="J33" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="L33" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="M33" s="24" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.6">
@@ -2671,17 +2699,27 @@
         <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="G34" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+      <c r="H34" t="s">
+        <v>281</v>
+      </c>
+      <c r="I34" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="J34" t="s">
+        <v>279</v>
       </c>
       <c r="L34" t="s">
-        <v>168</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="M34" s="24"/>
     </row>
     <row r="35" spans="1:13" ht="15.6">
       <c r="A35" s="2">
@@ -2699,16 +2737,28 @@
         <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>290</v>
       </c>
       <c r="G35" t="s">
-        <v>118</v>
-      </c>
-      <c r="M35" t="s">
-        <v>173</v>
+        <v>116</v>
+      </c>
+      <c r="H35" t="s">
+        <v>282</v>
+      </c>
+      <c r="I35" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="J35" t="s">
+        <v>292</v>
+      </c>
+      <c r="L35" t="s">
+        <v>166</v>
+      </c>
+      <c r="M35" s="24" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15.6">
@@ -2724,16 +2774,22 @@
         <v>Wed</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F36" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="G36" t="s">
+        <v>83</v>
       </c>
       <c r="L36" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="M36" s="24" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="16.2" thickBot="1">
@@ -2758,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L37" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.6">
@@ -2780,20 +2836,17 @@
         <v>10</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" t="s">
         <v>36</v>
       </c>
       <c r="L38" t="s">
-        <v>174</v>
-      </c>
-      <c r="M38" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.6">
@@ -2815,10 +2868,7 @@
         <v>37</v>
       </c>
       <c r="L39" t="s">
-        <v>175</v>
-      </c>
-      <c r="M39" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6">
@@ -2837,13 +2887,13 @@
         <v>35</v>
       </c>
       <c r="G40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L40" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6">
@@ -2862,16 +2912,13 @@
         <v>41</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L41" t="s">
-        <v>178</v>
-      </c>
-      <c r="M41" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6">
@@ -2887,22 +2934,22 @@
         <v>Wed</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G42" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L42" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.6">
@@ -2918,16 +2965,16 @@
         <v>Fri</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G43" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H43" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L43" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.6">
@@ -2946,19 +2993,22 @@
         <v>38</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G44" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H44" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L44" t="s">
-        <v>182</v>
+        <v>174</v>
+      </c>
+      <c r="M44" s="24" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.6">
@@ -2977,13 +3027,13 @@
         <v>42</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15.6">
@@ -3005,11 +3055,11 @@
         <v>5</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G46" s="9"/>
       <c r="L46" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="15.6">
@@ -3025,15 +3075,18 @@
         <v>Mon</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>4</v>
       </c>
       <c r="G47" s="18"/>
+      <c r="L47" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="48" spans="1:13" ht="15.6">
       <c r="A48" s="2">
@@ -3056,47 +3109,41 @@
       <c r="F48" t="s">
         <v>8</v>
       </c>
-      <c r="L48" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="L49" t="s">
-        <v>187</v>
-      </c>
-      <c r="M49" t="s">
-        <v>191</v>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="L50" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="14.4">
       <c r="A51" s="20"/>
       <c r="C51" s="21"/>
-      <c r="L51" t="s">
-        <v>190</v>
-      </c>
-      <c r="M51" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="52" spans="1:13" ht="14.4">
       <c r="B52" s="21"/>
-      <c r="M52" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
-      <c r="L54" t="s">
-        <v>192</v>
+      <c r="L52" t="s">
+        <v>183</v>
+      </c>
+      <c r="M52" s="24" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="L55" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="L59" t="s">
-        <v>195</v>
+        <v>185</v>
+      </c>
+      <c r="M55" s="24" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="L56" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="L60" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -3133,8 +3180,16 @@
     <hyperlink ref="I32" r:id="rId27" xr:uid="{7BBB8307-26C1-4A6B-A11B-C046A9E889A3}"/>
     <hyperlink ref="M33" r:id="rId28" xr:uid="{A99321CF-3833-4711-9272-617D4ADACDCC}"/>
     <hyperlink ref="I33" r:id="rId29" xr:uid="{90B349C4-33E9-4C05-A37C-6D393BD1852A}"/>
+    <hyperlink ref="I34" r:id="rId30" xr:uid="{B4B1FB19-A42A-409A-B51B-5F25103A0C02}"/>
+    <hyperlink ref="M35" r:id="rId31" xr:uid="{4808DC9C-9621-475A-912C-A4349B18342E}"/>
+    <hyperlink ref="M26" r:id="rId32" xr:uid="{90B7AFE8-10E2-4E37-B21B-86B368CCBC7D}"/>
+    <hyperlink ref="M36" r:id="rId33" xr:uid="{5157CB41-CD23-479F-BF03-7DCA0601E8C4}"/>
+    <hyperlink ref="M44" r:id="rId34" xr:uid="{5AEB11BA-66D4-4B88-98BE-7B30D51D6CE2}"/>
+    <hyperlink ref="M52" r:id="rId35" xr:uid="{4FB78D27-EA2B-47A6-BF6B-7AA3C15BE02F}"/>
+    <hyperlink ref="M55" r:id="rId36" xr:uid="{C679864C-F1BF-40AB-9F12-9EE67A0B581C}"/>
+    <hyperlink ref="I35" r:id="rId37" xr:uid="{F2225EC5-E8B7-4715-A3DD-E8C926AFFBE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="portrait" r:id="rId30"/>
+  <pageSetup scale="85" orientation="portrait" r:id="rId38"/>
 </worksheet>
 </file>
--- a/courses/Reg/DailyRecord.xlsx
+++ b/courses/Reg/DailyRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbarreto\Documents\GitHub\homepage\courses\Reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BA2E53-1B8A-445C-859E-973DA8C446F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016C9230-D97C-4A77-A810-C52738AFC992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="298">
   <si>
     <t>Grade</t>
   </si>
@@ -626,9 +626,6 @@
   </si>
   <si>
     <t>Lido Shuffle</t>
-  </si>
-  <si>
-    <t>Goodbye Earl</t>
   </si>
   <si>
     <t>Marvin</t>
@@ -1019,6 +1016,24 @@
   </si>
   <si>
     <t>Passcode: 0F?D%&amp;ZK</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/AVh7A6aYKWR4Twi_UZ7dfc4Qut6e6booRgzW0By3SoO4kv3D-pWpmULAXQgHF8Zo.bCoeqna39S-CU3R_</t>
+  </si>
+  <si>
+    <t>Passcode: ?QC8zKx+</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/tGrSNEymFO3ogf-oei11z8V8ddulOT5sPjSfary5hYx5nMwgr-M5QuasS9E4X6g_.nlfEFXpg0Dsf5MfF</t>
+  </si>
+  <si>
+    <t>Passcode: SD8WJqr?</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/OWscfjfqFkaoZKYHlRyKMnBlgtpO4KE1EOeRIciE3hmSt9oY0uN9uIkVO6uGHZY._X2ozq_jMlAXvrmi</t>
+  </si>
+  <si>
+    <t>Passcode: 2+ypYvp8</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1663,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16.2" thickBot="1">
@@ -1668,13 +1683,13 @@
         <v>12</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G4" s="23" t="s">
         <v>136</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I4" s="28" t="s">
         <v>141</v>
@@ -1702,13 +1717,13 @@
         <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
         <v>131</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I5" s="24" t="s">
         <v>142</v>
@@ -1717,7 +1732,7 @@
         <v>143</v>
       </c>
       <c r="L5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.6">
@@ -1739,19 +1754,19 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G6" t="s">
         <v>51</v>
       </c>
       <c r="H6" t="s">
+        <v>190</v>
+      </c>
+      <c r="I6" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="J6" t="s">
         <v>192</v>
-      </c>
-      <c r="J6" t="s">
-        <v>193</v>
       </c>
       <c r="L6" t="s">
         <v>145</v>
@@ -1776,19 +1791,19 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G7" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L7" t="s">
         <v>146</v>
@@ -1813,7 +1828,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G8" t="s">
         <v>53</v>
@@ -1822,10 +1837,10 @@
         <v>54</v>
       </c>
       <c r="I8" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="J8" t="s">
         <v>197</v>
-      </c>
-      <c r="J8" t="s">
-        <v>198</v>
       </c>
       <c r="L8" t="s">
         <v>147</v>
@@ -1859,10 +1874,10 @@
         <v>57</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L9" t="s">
         <v>148</v>
@@ -1890,7 +1905,7 @@
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F10" t="s">
         <v>59</v>
@@ -1899,19 +1914,19 @@
         <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L10" t="s">
+        <v>180</v>
+      </c>
+      <c r="M10" s="24" t="s">
         <v>181</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.6">
@@ -1939,13 +1954,13 @@
         <v>64</v>
       </c>
       <c r="H11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L11" t="s">
         <v>154</v>
@@ -1967,22 +1982,22 @@
         <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G12" t="s">
         <v>66</v>
       </c>
       <c r="H12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" t="s">
         <v>214</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="J12" t="s">
-        <v>215</v>
       </c>
       <c r="L12" t="s">
         <v>158</v>
@@ -2004,7 +2019,7 @@
         <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F13" t="s">
         <v>68</v>
@@ -2016,13 +2031,13 @@
         <v>70</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.6">
@@ -2053,10 +2068,10 @@
         <v>74</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L14" t="s">
         <v>156</v>
@@ -2087,13 +2102,13 @@
         <v>77</v>
       </c>
       <c r="H15" t="s">
+        <v>223</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="J15" t="s">
         <v>224</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="J15" t="s">
-        <v>225</v>
       </c>
       <c r="L15" t="s">
         <v>152</v>
@@ -2127,10 +2142,10 @@
         <v>80</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L16" t="s">
         <v>155</v>
@@ -2161,10 +2176,10 @@
         <v>83</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L17" t="s">
         <v>157</v>
@@ -2186,11 +2201,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G18" s="6"/>
       <c r="L18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6">
@@ -2212,25 +2227,25 @@
         <v>85</v>
       </c>
       <c r="F19" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" t="s">
+        <v>237</v>
+      </c>
+      <c r="H19" t="s">
+        <v>236</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="J19" t="s">
+        <v>234</v>
+      </c>
+      <c r="L19" t="s">
         <v>232</v>
       </c>
-      <c r="G19" t="s">
-        <v>238</v>
-      </c>
-      <c r="H19" t="s">
-        <v>237</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="J19" t="s">
-        <v>235</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>233</v>
-      </c>
-      <c r="M19" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6">
@@ -2255,19 +2270,19 @@
         <v>87</v>
       </c>
       <c r="G20" t="s">
+        <v>238</v>
+      </c>
+      <c r="H20" t="s">
         <v>239</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="J20" t="s">
         <v>240</v>
       </c>
-      <c r="I20" s="24" t="s">
+      <c r="L20" t="s">
         <v>242</v>
-      </c>
-      <c r="J20" t="s">
-        <v>241</v>
-      </c>
-      <c r="L20" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6">
@@ -2295,13 +2310,13 @@
         <v>91</v>
       </c>
       <c r="H21" t="s">
+        <v>244</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="J21" t="s">
         <v>245</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="J21" t="s">
-        <v>246</v>
       </c>
       <c r="L21" t="s">
         <v>160</v>
@@ -2335,10 +2350,10 @@
         <v>95</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L22" t="s">
         <v>161</v>
@@ -2360,22 +2375,22 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F23" t="s">
         <v>132</v>
       </c>
       <c r="G23" t="s">
+        <v>249</v>
+      </c>
+      <c r="H23" t="s">
         <v>250</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="J23" t="s">
         <v>251</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="J23" t="s">
-        <v>252</v>
       </c>
       <c r="L23" t="s">
         <v>159</v>
@@ -2397,7 +2412,7 @@
         <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F24" t="s">
         <v>133</v>
@@ -2406,13 +2421,13 @@
         <v>108</v>
       </c>
       <c r="H24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="J24" t="s">
         <v>255</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="J24" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6">
@@ -2431,25 +2446,25 @@
         <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G25" t="s">
         <v>107</v>
       </c>
       <c r="H25" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I25" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="J25" t="s">
+        <v>259</v>
+      </c>
+      <c r="L25" t="s">
         <v>261</v>
-      </c>
-      <c r="J25" t="s">
-        <v>260</v>
-      </c>
-      <c r="L25" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6">
@@ -2471,25 +2486,25 @@
         <v>109</v>
       </c>
       <c r="F26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G26" t="s">
+        <v>263</v>
+      </c>
+      <c r="H26" t="s">
+        <v>258</v>
+      </c>
+      <c r="I26" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="J26" t="s">
         <v>264</v>
       </c>
-      <c r="H26" t="s">
-        <v>259</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="J26" t="s">
-        <v>265</v>
-      </c>
       <c r="L26" t="s">
+        <v>169</v>
+      </c>
+      <c r="M26" s="24" t="s">
         <v>170</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6">
@@ -2508,7 +2523,7 @@
         <v>32</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F27" t="s">
         <v>134</v>
@@ -2517,16 +2532,16 @@
         <v>96</v>
       </c>
       <c r="H27" t="s">
+        <v>266</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="J27" t="s">
+        <v>269</v>
+      </c>
+      <c r="L27" t="s">
         <v>267</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="J27" t="s">
-        <v>270</v>
-      </c>
-      <c r="L27" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6">
@@ -2557,10 +2572,10 @@
         <v>114</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L28" t="s">
         <v>151</v>
@@ -2631,16 +2646,16 @@
         <v>110</v>
       </c>
       <c r="G32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H32" t="s">
         <v>113</v>
       </c>
       <c r="I32" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="J32" t="s">
         <v>274</v>
-      </c>
-      <c r="J32" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.6">
@@ -2668,19 +2683,19 @@
         <v>112</v>
       </c>
       <c r="H33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I33" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="J33" t="s">
         <v>276</v>
       </c>
-      <c r="J33" t="s">
-        <v>277</v>
-      </c>
       <c r="L33" t="s">
+        <v>177</v>
+      </c>
+      <c r="M33" s="24" t="s">
         <v>178</v>
-      </c>
-      <c r="M33" s="24" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.6">
@@ -2702,22 +2717,22 @@
         <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G34" t="s">
         <v>115</v>
       </c>
       <c r="H34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I34" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="J34" t="s">
         <v>278</v>
       </c>
-      <c r="J34" t="s">
+      <c r="L34" t="s">
         <v>279</v>
-      </c>
-      <c r="L34" t="s">
-        <v>280</v>
       </c>
       <c r="M34" s="24"/>
     </row>
@@ -2740,19 +2755,19 @@
         <v>118</v>
       </c>
       <c r="F35" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G35" t="s">
         <v>116</v>
       </c>
       <c r="H35" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I35" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="J35" t="s">
         <v>291</v>
-      </c>
-      <c r="J35" t="s">
-        <v>292</v>
       </c>
       <c r="L35" t="s">
         <v>166</v>
@@ -2785,11 +2800,17 @@
       <c r="G36" t="s">
         <v>83</v>
       </c>
+      <c r="I36" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="J36" t="s">
+        <v>293</v>
+      </c>
       <c r="L36" t="s">
+        <v>171</v>
+      </c>
+      <c r="M36" s="24" t="s">
         <v>172</v>
-      </c>
-      <c r="M36" s="24" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="16.2" thickBot="1">
@@ -2817,7 +2838,7 @@
         <v>125</v>
       </c>
       <c r="L37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.6">
@@ -2845,8 +2866,14 @@
       <c r="H38" t="s">
         <v>36</v>
       </c>
+      <c r="I38" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="J38" t="s">
+        <v>295</v>
+      </c>
       <c r="L38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.6">
@@ -2867,8 +2894,14 @@
       <c r="H39" t="s">
         <v>37</v>
       </c>
+      <c r="I39" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="J39" t="s">
+        <v>297</v>
+      </c>
       <c r="L39" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6">
@@ -2893,7 +2926,7 @@
         <v>124</v>
       </c>
       <c r="L40" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6">
@@ -2918,7 +2951,7 @@
         <v>102</v>
       </c>
       <c r="L41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6">
@@ -2948,9 +2981,6 @@
       <c r="H42" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="L42" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="43" spans="1:13" ht="15.6">
       <c r="A43" s="2">
@@ -2974,7 +3004,7 @@
         <v>129</v>
       </c>
       <c r="L43" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.6">
@@ -3005,10 +3035,7 @@
         <v>128</v>
       </c>
       <c r="L44" t="s">
-        <v>174</v>
-      </c>
-      <c r="M44" s="24" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.6">
@@ -3033,7 +3060,10 @@
         <v>102</v>
       </c>
       <c r="L45" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="M45" s="24" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15.6">
@@ -3059,7 +3089,7 @@
       </c>
       <c r="G46" s="9"/>
       <c r="L46" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="15.6">
@@ -3085,7 +3115,7 @@
       </c>
       <c r="G47" s="18"/>
       <c r="L47" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15.6">
@@ -3112,7 +3142,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="L50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="14.4">
@@ -3122,28 +3152,28 @@
     <row r="52" spans="1:13" ht="14.4">
       <c r="B52" s="21"/>
       <c r="L52" t="s">
+        <v>182</v>
+      </c>
+      <c r="M52" s="24" t="s">
         <v>183</v>
-      </c>
-      <c r="M52" s="24" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="L55" t="s">
+        <v>184</v>
+      </c>
+      <c r="M55" s="24" t="s">
         <v>185</v>
-      </c>
-      <c r="M55" s="24" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="L56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="L60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3184,12 +3214,18 @@
     <hyperlink ref="M35" r:id="rId31" xr:uid="{4808DC9C-9621-475A-912C-A4349B18342E}"/>
     <hyperlink ref="M26" r:id="rId32" xr:uid="{90B7AFE8-10E2-4E37-B21B-86B368CCBC7D}"/>
     <hyperlink ref="M36" r:id="rId33" xr:uid="{5157CB41-CD23-479F-BF03-7DCA0601E8C4}"/>
-    <hyperlink ref="M44" r:id="rId34" xr:uid="{5AEB11BA-66D4-4B88-98BE-7B30D51D6CE2}"/>
+    <hyperlink ref="M45" r:id="rId34" xr:uid="{5AEB11BA-66D4-4B88-98BE-7B30D51D6CE2}"/>
     <hyperlink ref="M52" r:id="rId35" xr:uid="{4FB78D27-EA2B-47A6-BF6B-7AA3C15BE02F}"/>
     <hyperlink ref="M55" r:id="rId36" xr:uid="{C679864C-F1BF-40AB-9F12-9EE67A0B581C}"/>
     <hyperlink ref="I35" r:id="rId37" xr:uid="{F2225EC5-E8B7-4715-A3DD-E8C926AFFBE9}"/>
+    <hyperlink ref="I36" r:id="rId38" xr:uid="{3191F546-109F-40A5-B0B8-48A63054C6DC}"/>
+    <hyperlink ref="I38" r:id="rId39" xr:uid="{7F488FF9-D4C9-4DFD-B169-AAE599D57542}"/>
+    <hyperlink ref="I39" r:id="rId40" xr:uid="{5A6D8735-3851-4571-89F6-B6E871265ABD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="portrait" r:id="rId38"/>
+  <pageSetup scale="85" orientation="portrait" r:id="rId41"/>
+  <ignoredErrors>
+    <ignoredError sqref="A38 A41 A44 A47" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/courses/Reg/DailyRecord.xlsx
+++ b/courses/Reg/DailyRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbarreto\Documents\GitHub\homepage\courses\Reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016C9230-D97C-4A77-A810-C52738AFC992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA7373B-C5AB-4875-8D2B-570DDA67DF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="257">
   <si>
     <t>Grade</t>
   </si>
@@ -132,9 +132,6 @@
     <t>Multivariate Regression Workshop</t>
   </si>
   <si>
-    <t>FALL BREAK</t>
-  </si>
-  <si>
     <t>Confidence Intervals</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
   </si>
   <si>
     <t>i.firmsize</t>
-  </si>
-  <si>
-    <t>Complex Surveys and Unequal Probability of Selection</t>
   </si>
   <si>
     <r>
@@ -220,9 +214,6 @@
   </si>
   <si>
     <t>Heteroskedasticity: GLS</t>
-  </si>
-  <si>
-    <t>BUS 305: Regression with Microdata</t>
   </si>
   <si>
     <t>Syllabus, Basic stats on INCWAGE, avg is min SSR</t>
@@ -480,9 +471,6 @@
     <t>Reg results table</t>
   </si>
   <si>
-    <t>33.pdf</t>
-  </si>
-  <si>
     <t>Use SAMPLE, sim</t>
   </si>
   <si>
@@ -490,15 +478,6 @@
   </si>
   <si>
     <t>Study</t>
-  </si>
-  <si>
-    <t>Orthoreg.xlsm</t>
-  </si>
-  <si>
-    <t>EqualUnequalProb.xlsm</t>
-  </si>
-  <si>
-    <t>Matriculation.xlsx</t>
   </si>
   <si>
     <t>In Excel file</t>
@@ -553,138 +532,6 @@
     <t>Passcode: E+a46@yb</t>
   </si>
   <si>
-    <t>Song</t>
-  </si>
-  <si>
-    <t>Pitbull Guantanamera</t>
-  </si>
-  <si>
-    <t>Irakere Marie Laveaux</t>
-  </si>
-  <si>
-    <t>Viene a pedir mi mano</t>
-  </si>
-  <si>
-    <t>Chan Chan</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=tGbRZ73NvlY</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=o5cELP06Mik&amp;t=2s</t>
-  </si>
-  <si>
-    <t>Telephone Line</t>
-  </si>
-  <si>
-    <t>El Cuarto de Tula video</t>
-  </si>
-  <si>
-    <t>One tin soldier video</t>
-  </si>
-  <si>
-    <t>Let's Stay Together</t>
-  </si>
-  <si>
-    <t>Mi Tierra</t>
-  </si>
-  <si>
-    <t>This Land is Your Land</t>
-  </si>
-  <si>
-    <t>Cuban Elvis</t>
-  </si>
-  <si>
-    <t>Guantanamera</t>
-  </si>
-  <si>
-    <t>Ojala que llueva café</t>
-  </si>
-  <si>
-    <t>Body Electric</t>
-  </si>
-  <si>
-    <t>Picabo Street skiing video</t>
-  </si>
-  <si>
-    <t>rocky raccoon</t>
-  </si>
-  <si>
-    <t>Fire on High</t>
-  </si>
-  <si>
-    <t>City of New Orleans</t>
-  </si>
-  <si>
-    <t>Heart of Gold</t>
-  </si>
-  <si>
-    <t>Band of Gold</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=jhuDgUnqXUY&amp;t=16s</t>
-  </si>
-  <si>
-    <t>Lido Shuffle</t>
-  </si>
-  <si>
-    <t>Marvin</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=FrkEDe6Ljqs</t>
-  </si>
-  <si>
-    <t>Black or White</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=F2AitTPI5U0</t>
-  </si>
-  <si>
-    <t>Ode to Joy</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=kbJcQYVtZMo&amp;t=2s</t>
-  </si>
-  <si>
-    <t>Oye Como Va</t>
-  </si>
-  <si>
-    <t>Light My Fire</t>
-  </si>
-  <si>
-    <t>Get Ready</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=A3Ix4hKSnxQ</t>
-  </si>
-  <si>
-    <t>Everyday People</t>
-  </si>
-  <si>
-    <t>Fast Car Grammys</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=pLfH9HSUyf4</t>
-  </si>
-  <si>
-    <t>Texas Hold Em</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ycwtqqhV6UE</t>
-  </si>
-  <si>
-    <t>Shaft</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ZVj8FgMMAK8&amp;t=96s</t>
-  </si>
-  <si>
-    <t>Long and Winding Road</t>
-  </si>
-  <si>
-    <t>Southern Cross</t>
-  </si>
-  <si>
     <t>1.JourneyBegins</t>
   </si>
   <si>
@@ -725,9 +572,6 @@
   </si>
   <si>
     <t>1.CPSIncEducPreClass.xlsx</t>
-  </si>
-  <si>
-    <t>Every day has student and teacher Word doc</t>
   </si>
   <si>
     <t>Class Prep Notes</t>
@@ -770,9 +614,6 @@
     <t>https://depauw-edu.zoom.us/rec/share/8Ma03tb3qOC9X03KZ17FYqKAz42Jq1JklNBBzrMbhC7IZA-CA5irvVA6kClhJBkc.L4L-5dPo2Fzoaj0C</t>
   </si>
   <si>
-    <t>La Bamba</t>
-  </si>
-  <si>
     <t>Discuss OVB, Add Exp and Exp^2</t>
   </si>
   <si>
@@ -818,12 +659,6 @@
     <t>15.Measurement Error</t>
   </si>
   <si>
-    <t>Night Fever video</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=e6GB04zeDeQ</t>
-  </si>
-  <si>
     <t>Passcode: 3K5y!N+J</t>
   </si>
   <si>
@@ -848,12 +683,6 @@
     <t>https://depauw-edu.zoom.us/rec/share/0QFyjU17rgqnlj5vOEt17WY-MUKPq4s-RjiO1LflEFJPqIsVG0Q7UjRRUMXeDj6Q.Uks4lVawUOXYbB-a</t>
   </si>
   <si>
-    <t>zoom</t>
-  </si>
-  <si>
-    <t>exam</t>
-  </si>
-  <si>
     <t>Use a student's file (or 17.PreClass), save as to public folder</t>
   </si>
   <si>
@@ -905,9 +734,6 @@
     <t>https://depauw-edu.zoom.us/rec/share/uxfne8g5W8Iz48l9w14vDzOOknTC_9UrMp2YGeC16WwmrqScIE1mwLzQ-d1nPz3V.WlxMe0_ginZ5YeQy</t>
   </si>
   <si>
-    <t>air media would not play it after I adjusted the volume</t>
-  </si>
-  <si>
     <t>22 all of it</t>
   </si>
   <si>
@@ -923,9 +749,6 @@
     <t>Use 23.SEPreClass</t>
   </si>
   <si>
-    <t>Kodachrome</t>
-  </si>
-  <si>
     <t>68% CI with n=5 and n=100, understand Est SE and t dist</t>
   </si>
   <si>
@@ -957,9 +780,6 @@
   </si>
   <si>
     <t>Passcode: r%k2Fr!*</t>
-  </si>
-  <si>
-    <t>Il Paradisi</t>
   </si>
   <si>
     <t>Use 27.HetPreClass</t>
@@ -1034,6 +854,63 @@
   </si>
   <si>
     <t>Passcode: 2+ypYvp8</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/e_tnBj9TPBpDpJwk-M58NZFEMtq_gGstEBvRMubEQ2hXFlTkV2Ews-c_58hF0N3j.YViq6NRYyDEZQgFR</t>
+  </si>
+  <si>
+    <t>Passcode: Jdq%n7Cx</t>
+  </si>
+  <si>
+    <t>30.Partial Xs</t>
+  </si>
+  <si>
+    <t>36.Matriculation.xlsx</t>
+  </si>
+  <si>
+    <t>37.EqualUnequalProb.xlsm</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/LrwL07QRW0DCiQMSJT5SRdssv4ErCniVigzjECF2d8M_D4SxtHmUtl2R5s4jG2gv.DNPgpryXz8k_cGg6</t>
+  </si>
+  <si>
+    <t>Passcode: bd1^b8dU</t>
+  </si>
+  <si>
+    <t>35.Orthoreg.xlsm</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/IwJ29UkeOmKYMlhZXAEuajxRM2L7c2IIz4sQtigcf2x0ClN6gcy1j0GZUYMkb3gu.MH7NP4YOVcxQZjqy</t>
+  </si>
+  <si>
+    <t>Passcode: g55@@DW3</t>
+  </si>
+  <si>
+    <t>https://depauw-edu.zoom.us/rec/share/yfj8mnMWkXOUWwFr4LfZTgwOGDhNics2MNMR6Hd_8nLPcwC7_X2tFP7vLIBNsp7X.33YPJqqqXbJVfQRM</t>
+  </si>
+  <si>
+    <t>Passcode: pp@1HK.k</t>
+  </si>
+  <si>
+    <t>SPRING BREAK</t>
+  </si>
+  <si>
+    <t>Unequal Probability of Selection and WLS</t>
+  </si>
+  <si>
+    <t>BUSA 305: Regression with Microdata</t>
+  </si>
+  <si>
+    <t>Most classes have a student Word doc handout (see Google drive folder)</t>
+  </si>
+  <si>
+    <t>SPRING 2026 VERSION</t>
+  </si>
+  <si>
+    <t>Print A1:D48 for last day</t>
+  </si>
+  <si>
+    <t>copy/paste just the passcode itself</t>
   </si>
 </sst>
 </file>
@@ -1630,7 +1507,7 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="11.4"/>
   <cols>
     <col min="3" max="3" width="8.625" customWidth="1"/>
@@ -1638,35 +1515,39 @@
     <col min="5" max="5" width="59" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="27.75" customWidth="1"/>
-    <col min="8" max="8" width="58.75" customWidth="1"/>
-    <col min="9" max="9" width="11.75" customWidth="1"/>
+    <col min="8" max="8" width="62.875" customWidth="1"/>
+    <col min="9" max="9" width="24.625" customWidth="1"/>
+    <col min="10" max="10" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.399999999999999">
+    <row r="1" spans="1:11" ht="17.399999999999999">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>252</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:18" ht="13.2">
+      <c r="E1" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="13.2">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:11">
       <c r="A3" s="24" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="16.2" thickBot="1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16.2" thickBot="1">
       <c r="A4" s="12" t="s">
         <v>6</v>
       </c>
@@ -1683,23 +1564,20 @@
         <v>12</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>286</v>
+        <v>226</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J4" s="28"/>
-      <c r="L4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="15.6">
+    </row>
+    <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="2">
         <v>46048</v>
       </c>
@@ -1711,31 +1589,31 @@
         <v>Mon</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="J5" t="s">
-        <v>143</v>
-      </c>
-      <c r="L5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="15.6">
+        <v>136</v>
+      </c>
+      <c r="K5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.6">
       <c r="A6" s="2">
         <f>A5+2</f>
         <v>46050</v>
@@ -1754,25 +1632,22 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="J6" t="s">
-        <v>192</v>
-      </c>
-      <c r="L6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="24">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="24">
       <c r="A7" s="2">
         <f>A6+2</f>
         <v>46052</v>
@@ -1791,25 +1666,22 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="J7" t="s">
-        <v>194</v>
-      </c>
-      <c r="L7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="15.6">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.6">
       <c r="A8" s="2">
         <f>A5+7</f>
         <v>46055</v>
@@ -1828,25 +1700,22 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="J8" t="s">
-        <v>197</v>
-      </c>
-      <c r="L8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="15.6">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.6">
       <c r="A9" s="2">
         <f t="shared" ref="A9:A15" si="1">A6+7</f>
         <v>46057</v>
@@ -1865,31 +1734,22 @@
         <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="J9" t="s">
-        <v>199</v>
-      </c>
-      <c r="L9" t="s">
         <v>148</v>
       </c>
-      <c r="M9" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="R9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.6">
+    </row>
+    <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="2">
         <f t="shared" si="1"/>
         <v>46059</v>
@@ -1902,34 +1762,28 @@
         <v>Fri</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H10" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="J10" t="s">
-        <v>207</v>
-      </c>
-      <c r="L10" t="s">
-        <v>180</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="15.6">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.6">
       <c r="A11" s="2">
         <f t="shared" si="1"/>
         <v>46062</v>
@@ -1942,31 +1796,28 @@
         <v>Mon</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" t="s">
-        <v>64</v>
-      </c>
       <c r="H11" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="J11" t="s">
-        <v>209</v>
-      </c>
-      <c r="L11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="15.6">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="2">
         <f t="shared" si="1"/>
         <v>46064</v>
@@ -1979,31 +1830,28 @@
         <v>Wed</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="F12" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H12" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="J12" t="s">
-        <v>214</v>
-      </c>
-      <c r="L12" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="15.6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.6">
       <c r="A13" s="2">
         <f t="shared" si="1"/>
         <v>46066</v>
@@ -2016,31 +1864,28 @@
         <v>Fri</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
         <v>67</v>
       </c>
-      <c r="E13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" t="s">
-        <v>70</v>
-      </c>
       <c r="I13" s="24" t="s">
-        <v>220</v>
+        <v>167</v>
       </c>
       <c r="J13" t="s">
-        <v>219</v>
-      </c>
-      <c r="L13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="15.6">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.6">
       <c r="A14" s="2">
         <f t="shared" si="1"/>
         <v>46069</v>
@@ -2056,28 +1901,25 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
         <v>71</v>
       </c>
-      <c r="F14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" t="s">
-        <v>74</v>
-      </c>
       <c r="I14" s="24" t="s">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="J14" t="s">
-        <v>221</v>
-      </c>
-      <c r="L14" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="15.6">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.6">
       <c r="A15" s="2">
         <f t="shared" si="1"/>
         <v>46071</v>
@@ -2090,31 +1932,28 @@
         <v>Wed</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="J15" t="s">
-        <v>224</v>
-      </c>
-      <c r="L15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="15.6">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.6">
       <c r="A16" s="2">
         <f>A15+2</f>
         <v>46073</v>
@@ -2133,25 +1972,22 @@
         <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="J16" t="s">
-        <v>226</v>
-      </c>
-      <c r="L16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="15.6">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.6">
       <c r="A17" s="2">
         <f>A16+3</f>
         <v>46076</v>
@@ -2164,28 +2000,25 @@
         <v>Mon</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>228</v>
-      </c>
-      <c r="L17" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15.6">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.6">
       <c r="A18" s="2">
         <f>A17+2</f>
         <v>46078</v>
@@ -2201,14 +2034,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="L18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="15.6">
+    </row>
+    <row r="19" spans="1:10" ht="15.6">
       <c r="A19" s="2">
         <f>A18+2</f>
         <v>46080</v>
@@ -2221,34 +2051,28 @@
         <v>Fri</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="G19" t="s">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="H19" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="J19" t="s">
-        <v>234</v>
-      </c>
-      <c r="L19" t="s">
-        <v>232</v>
-      </c>
-      <c r="M19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="15.6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.6">
       <c r="A20" s="2">
         <f>A17+7</f>
         <v>46083</v>
@@ -2264,28 +2088,25 @@
         <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>238</v>
+        <v>183</v>
       </c>
       <c r="H20" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>240</v>
-      </c>
-      <c r="L20" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="15.6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.6">
       <c r="A21" s="2">
         <f>A18+7</f>
         <v>46085</v>
@@ -2298,31 +2119,28 @@
         <v>Wed</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" t="s">
         <v>88</v>
       </c>
-      <c r="E21" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" t="s">
-        <v>91</v>
-      </c>
       <c r="H21" t="s">
-        <v>244</v>
+        <v>187</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="J21" t="s">
-        <v>245</v>
-      </c>
-      <c r="L21" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15.6">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.6">
       <c r="A22" s="2">
         <f>A21+2</f>
         <v>46087</v>
@@ -2338,28 +2156,25 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s">
         <v>92</v>
       </c>
-      <c r="F22" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" t="s">
-        <v>95</v>
-      </c>
       <c r="I22" s="24" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="J22" t="s">
-        <v>247</v>
-      </c>
-      <c r="L22" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.6">
       <c r="A23" s="2">
         <f>A22+3</f>
         <v>46090</v>
@@ -2375,28 +2190,25 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="F23" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G23" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="H23" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="J23" t="s">
-        <v>251</v>
-      </c>
-      <c r="L23" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15.6">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.6">
       <c r="A24" s="2">
         <f>A23+2</f>
         <v>46092</v>
@@ -2412,25 +2224,25 @@
         <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>283</v>
+        <v>223</v>
       </c>
       <c r="F24" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H24" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="J24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="15.6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.6">
       <c r="A25" s="2">
         <f>A24+2</f>
         <v>46094</v>
@@ -2446,28 +2258,25 @@
         <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="F25" t="s">
-        <v>262</v>
+        <v>204</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H25" t="s">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>260</v>
+        <v>203</v>
       </c>
       <c r="J25" t="s">
-        <v>259</v>
-      </c>
-      <c r="L25" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="15.6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.6">
       <c r="A26" s="2">
         <f>A25+3</f>
         <v>46097</v>
@@ -2483,31 +2292,25 @@
         <v>30</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F26" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="G26" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="H26" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>265</v>
+        <v>207</v>
       </c>
       <c r="J26" t="s">
-        <v>264</v>
-      </c>
-      <c r="L26" t="s">
-        <v>169</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15.6">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.6">
       <c r="A27" s="2">
         <f>A26+2</f>
         <v>46099</v>
@@ -2520,31 +2323,28 @@
         <v>Wed</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="F27" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="J27" t="s">
-        <v>269</v>
-      </c>
-      <c r="L27" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.6">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.6">
       <c r="A28" s="2">
         <f>A27+2</f>
         <v>46101</v>
@@ -2557,32 +2357,28 @@
         <v>Fri</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>272</v>
+        <v>213</v>
       </c>
       <c r="J28" t="s">
-        <v>271</v>
-      </c>
-      <c r="L28" t="s">
-        <v>151</v>
-      </c>
-      <c r="M28" s="24"/>
-    </row>
-    <row r="29" spans="1:13" ht="15.6">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.6">
       <c r="A29" s="2">
         <f>A28+3</f>
         <v>46104</v>
@@ -2593,10 +2389,10 @@
         <v>Mon</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.6">
       <c r="A30" s="2">
         <f>A29+2</f>
         <v>46106</v>
@@ -2607,10 +2403,10 @@
         <v>Wed</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.6">
       <c r="A31" s="2">
         <f>A30+2</f>
         <v>46108</v>
@@ -2621,10 +2417,10 @@
         <v>Fri</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.6">
       <c r="A32" s="2">
         <f>A31+3</f>
         <v>46111</v>
@@ -2637,28 +2433,28 @@
         <v>Mon</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" t="s">
+        <v>227</v>
+      </c>
+      <c r="H32" t="s">
         <v>110</v>
       </c>
-      <c r="G32" t="s">
-        <v>287</v>
-      </c>
-      <c r="H32" t="s">
-        <v>113</v>
-      </c>
       <c r="I32" s="27" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="J32" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.6">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.6">
       <c r="A33" s="2">
         <f>A32+2</f>
         <v>46113</v>
@@ -2671,34 +2467,28 @@
         <v>Wed</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F33" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H33" t="s">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="J33" t="s">
-        <v>276</v>
-      </c>
-      <c r="L33" t="s">
-        <v>177</v>
-      </c>
-      <c r="M33" s="24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.6">
       <c r="A34" s="2">
         <f>A33+2</f>
         <v>46115</v>
@@ -2711,32 +2501,28 @@
         <v>Fri</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>288</v>
+        <v>228</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H34" t="s">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="I34" s="27" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="J34" t="s">
-        <v>278</v>
-      </c>
-      <c r="L34" t="s">
-        <v>279</v>
-      </c>
-      <c r="M34" s="24"/>
-    </row>
-    <row r="35" spans="1:13" ht="15.6">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.6">
       <c r="A35" s="2">
         <f>A34+3</f>
         <v>46118</v>
@@ -2749,34 +2535,28 @@
         <v>Mon</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F35" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="G35" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H35" t="s">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="I35" s="27" t="s">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="J35" t="s">
-        <v>291</v>
-      </c>
-      <c r="L35" t="s">
-        <v>166</v>
-      </c>
-      <c r="M35" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.6">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.6">
       <c r="A36" s="2">
         <f>A35+2</f>
         <v>46120</v>
@@ -2789,31 +2569,25 @@
         <v>Wed</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F36" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I36" s="27" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="J36" t="s">
-        <v>293</v>
-      </c>
-      <c r="L36" t="s">
-        <v>171</v>
-      </c>
-      <c r="M36" s="24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="16.2" thickBot="1">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="16.2" thickBot="1">
       <c r="A37" s="2">
         <f>A36+2</f>
         <v>46122</v>
@@ -2829,19 +2603,16 @@
         <v>2</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L37" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.6">
       <c r="A38" s="2">
         <f>A37+3</f>
         <v>46125</v>
@@ -2857,26 +2628,23 @@
         <v>10</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I38" s="27" t="s">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="J38" t="s">
-        <v>295</v>
-      </c>
-      <c r="L38" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.6">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.6">
       <c r="A39" s="2">
         <f>A38+2</f>
         <v>46127</v>
@@ -2892,19 +2660,16 @@
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I39" s="27" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="J39" t="s">
-        <v>297</v>
-      </c>
-      <c r="L39" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.6">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.6">
       <c r="A40" s="2">
         <f>A39+2</f>
         <v>46129</v>
@@ -2917,19 +2682,22 @@
         <v>Fri</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G40" t="s">
-        <v>123</v>
+        <v>240</v>
       </c>
       <c r="H40" t="s">
-        <v>124</v>
-      </c>
-      <c r="L40" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.6">
+        <v>120</v>
+      </c>
+      <c r="I40" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="J40" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.6">
       <c r="A41" s="2">
         <f>A40+3</f>
         <v>46132</v>
@@ -2942,19 +2710,16 @@
         <v>Mon</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="L41" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.6">
       <c r="A42" s="2">
         <f>A41+2</f>
         <v>46134</v>
@@ -2967,22 +2732,28 @@
         <v>Wed</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G42" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.6">
+        <v>245</v>
+      </c>
+      <c r="I42" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="J42" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.6">
       <c r="A43" s="2">
         <f>A42+2</f>
         <v>46136</v>
@@ -2995,19 +2766,22 @@
         <v>Fri</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H43" t="s">
-        <v>129</v>
-      </c>
-      <c r="L43" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="15.6">
+        <v>241</v>
+      </c>
+      <c r="I43" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="J43" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.6">
       <c r="A44" s="2">
         <f>A43+3</f>
         <v>46139</v>
@@ -3020,25 +2794,28 @@
         <v>Mon</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>38</v>
+        <v>251</v>
       </c>
       <c r="E44" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G44" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H44" t="s">
-        <v>128</v>
-      </c>
-      <c r="L44" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="15.6">
+        <v>242</v>
+      </c>
+      <c r="I44" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="J44" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.6">
       <c r="A45" s="2">
         <f>A44+2</f>
         <v>46141</v>
@@ -3051,22 +2828,16 @@
         <v>Wed</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="L45" t="s">
-        <v>173</v>
-      </c>
-      <c r="M45" s="24" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="15.6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.6">
       <c r="A46" s="14">
         <f>A45+2</f>
         <v>46143</v>
@@ -3085,14 +2856,11 @@
         <v>5</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G46" s="9"/>
-      <c r="L46" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="15.6">
+    </row>
+    <row r="47" spans="1:10" ht="15.6">
       <c r="A47" s="2">
         <f>A46+3</f>
         <v>46146</v>
@@ -3105,20 +2873,17 @@
         <v>Mon</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>4</v>
       </c>
       <c r="G47" s="18"/>
-      <c r="L47" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="15.6">
+    </row>
+    <row r="48" spans="1:10" ht="15.6">
       <c r="A48" s="2">
         <f>A47+2</f>
         <v>46148</v>
@@ -3131,50 +2896,24 @@
         <v>Wed</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="L50" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="14.4">
+      <c r="G48" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="14.4">
       <c r="A51" s="20"/>
       <c r="C51" s="21"/>
     </row>
-    <row r="52" spans="1:13" ht="14.4">
+    <row r="52" spans="1:3" ht="14.4">
       <c r="B52" s="21"/>
-      <c r="L52" t="s">
-        <v>182</v>
-      </c>
-      <c r="M52" s="24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="L55" t="s">
-        <v>184</v>
-      </c>
-      <c r="M55" s="24" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="L56" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
-      <c r="L60" t="s">
-        <v>187</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3187,43 +2926,38 @@
     <hyperlink ref="I7" r:id="rId4" xr:uid="{510B6558-56CD-44A2-805A-B2C7949FF8EF}"/>
     <hyperlink ref="I8" r:id="rId5" xr:uid="{8F594743-93A9-4665-95A9-83C99405E5BD}"/>
     <hyperlink ref="I9" r:id="rId6" xr:uid="{22CA0FDC-A63D-456F-81DA-74E9A89775EE}"/>
-    <hyperlink ref="M9" r:id="rId7" xr:uid="{57DEC4EF-2D00-4E8D-9A77-300474F2F32A}"/>
-    <hyperlink ref="M10" r:id="rId8" xr:uid="{FEFB366C-46B5-4FCF-B20A-B66880D0CBB0}"/>
-    <hyperlink ref="I10" r:id="rId9" xr:uid="{81DBC2F5-857F-40BD-8614-8B92975625C0}"/>
-    <hyperlink ref="I11" r:id="rId10" xr:uid="{9DB554BE-F1E7-4A10-8857-6AD7EE61C4F9}"/>
-    <hyperlink ref="I12" r:id="rId11" xr:uid="{A0BE5509-76CC-47EB-8F87-CE802986609C}"/>
-    <hyperlink ref="I13" r:id="rId12" xr:uid="{17E1DBA7-1282-4B9C-AE93-3520A2CC1B70}"/>
-    <hyperlink ref="I14" r:id="rId13" xr:uid="{B2838FD0-63F6-4E7A-BA3A-876EF84E7420}"/>
-    <hyperlink ref="I15" r:id="rId14" xr:uid="{284CEF5E-CA76-42E6-ABDD-B2562CA15DD5}"/>
-    <hyperlink ref="I16" r:id="rId15" xr:uid="{740748D9-3731-4D44-90E6-D444B3DFFCDA}"/>
-    <hyperlink ref="I17" r:id="rId16" xr:uid="{66888497-A698-4D0D-A51C-3F6EF823B9DB}"/>
-    <hyperlink ref="I19" r:id="rId17" xr:uid="{4AC4DC58-D110-49BA-AE55-2D0EC7976090}"/>
-    <hyperlink ref="I20" r:id="rId18" xr:uid="{A4C4F584-67AC-4B2D-9137-C45F31F04441}"/>
-    <hyperlink ref="I21" r:id="rId19" xr:uid="{266AF027-98B3-4D9C-8AB8-C8B1B42BAD7B}"/>
-    <hyperlink ref="I22" r:id="rId20" xr:uid="{FEC1AA73-808D-4A29-9E5F-50B1A3E7721F}"/>
-    <hyperlink ref="I23" r:id="rId21" xr:uid="{8B44EAEB-E310-4371-8C4C-2F58A07E7C87}"/>
-    <hyperlink ref="I24" r:id="rId22" xr:uid="{3942BA65-4836-4C7A-95F8-6C4B19B38220}"/>
-    <hyperlink ref="I25" r:id="rId23" xr:uid="{EB0A94FC-1253-44E8-A838-2C52B3979496}"/>
-    <hyperlink ref="I26" r:id="rId24" xr:uid="{BFEB963A-7643-41BF-9C5D-4A5452BD9A9D}"/>
-    <hyperlink ref="I27" r:id="rId25" xr:uid="{F3195E4E-9BDD-4125-BBD6-A00170E588CA}"/>
-    <hyperlink ref="I28" r:id="rId26" xr:uid="{A7A55F02-5B29-4375-AB5F-BE0C0B59FFE1}"/>
-    <hyperlink ref="I32" r:id="rId27" xr:uid="{7BBB8307-26C1-4A6B-A11B-C046A9E889A3}"/>
-    <hyperlink ref="M33" r:id="rId28" xr:uid="{A99321CF-3833-4711-9272-617D4ADACDCC}"/>
-    <hyperlink ref="I33" r:id="rId29" xr:uid="{90B349C4-33E9-4C05-A37C-6D393BD1852A}"/>
-    <hyperlink ref="I34" r:id="rId30" xr:uid="{B4B1FB19-A42A-409A-B51B-5F25103A0C02}"/>
-    <hyperlink ref="M35" r:id="rId31" xr:uid="{4808DC9C-9621-475A-912C-A4349B18342E}"/>
-    <hyperlink ref="M26" r:id="rId32" xr:uid="{90B7AFE8-10E2-4E37-B21B-86B368CCBC7D}"/>
-    <hyperlink ref="M36" r:id="rId33" xr:uid="{5157CB41-CD23-479F-BF03-7DCA0601E8C4}"/>
-    <hyperlink ref="M45" r:id="rId34" xr:uid="{5AEB11BA-66D4-4B88-98BE-7B30D51D6CE2}"/>
-    <hyperlink ref="M52" r:id="rId35" xr:uid="{4FB78D27-EA2B-47A6-BF6B-7AA3C15BE02F}"/>
-    <hyperlink ref="M55" r:id="rId36" xr:uid="{C679864C-F1BF-40AB-9F12-9EE67A0B581C}"/>
-    <hyperlink ref="I35" r:id="rId37" xr:uid="{F2225EC5-E8B7-4715-A3DD-E8C926AFFBE9}"/>
-    <hyperlink ref="I36" r:id="rId38" xr:uid="{3191F546-109F-40A5-B0B8-48A63054C6DC}"/>
-    <hyperlink ref="I38" r:id="rId39" xr:uid="{7F488FF9-D4C9-4DFD-B169-AAE599D57542}"/>
-    <hyperlink ref="I39" r:id="rId40" xr:uid="{5A6D8735-3851-4571-89F6-B6E871265ABD}"/>
+    <hyperlink ref="I10" r:id="rId7" xr:uid="{81DBC2F5-857F-40BD-8614-8B92975625C0}"/>
+    <hyperlink ref="I11" r:id="rId8" xr:uid="{9DB554BE-F1E7-4A10-8857-6AD7EE61C4F9}"/>
+    <hyperlink ref="I12" r:id="rId9" xr:uid="{A0BE5509-76CC-47EB-8F87-CE802986609C}"/>
+    <hyperlink ref="I13" r:id="rId10" xr:uid="{17E1DBA7-1282-4B9C-AE93-3520A2CC1B70}"/>
+    <hyperlink ref="I14" r:id="rId11" xr:uid="{B2838FD0-63F6-4E7A-BA3A-876EF84E7420}"/>
+    <hyperlink ref="I15" r:id="rId12" xr:uid="{284CEF5E-CA76-42E6-ABDD-B2562CA15DD5}"/>
+    <hyperlink ref="I16" r:id="rId13" xr:uid="{740748D9-3731-4D44-90E6-D444B3DFFCDA}"/>
+    <hyperlink ref="I17" r:id="rId14" xr:uid="{66888497-A698-4D0D-A51C-3F6EF823B9DB}"/>
+    <hyperlink ref="I19" r:id="rId15" xr:uid="{4AC4DC58-D110-49BA-AE55-2D0EC7976090}"/>
+    <hyperlink ref="I20" r:id="rId16" xr:uid="{A4C4F584-67AC-4B2D-9137-C45F31F04441}"/>
+    <hyperlink ref="I21" r:id="rId17" xr:uid="{266AF027-98B3-4D9C-8AB8-C8B1B42BAD7B}"/>
+    <hyperlink ref="I22" r:id="rId18" xr:uid="{FEC1AA73-808D-4A29-9E5F-50B1A3E7721F}"/>
+    <hyperlink ref="I23" r:id="rId19" xr:uid="{8B44EAEB-E310-4371-8C4C-2F58A07E7C87}"/>
+    <hyperlink ref="I24" r:id="rId20" xr:uid="{3942BA65-4836-4C7A-95F8-6C4B19B38220}"/>
+    <hyperlink ref="I25" r:id="rId21" xr:uid="{EB0A94FC-1253-44E8-A838-2C52B3979496}"/>
+    <hyperlink ref="I26" r:id="rId22" xr:uid="{BFEB963A-7643-41BF-9C5D-4A5452BD9A9D}"/>
+    <hyperlink ref="I27" r:id="rId23" xr:uid="{F3195E4E-9BDD-4125-BBD6-A00170E588CA}"/>
+    <hyperlink ref="I28" r:id="rId24" xr:uid="{A7A55F02-5B29-4375-AB5F-BE0C0B59FFE1}"/>
+    <hyperlink ref="I32" r:id="rId25" xr:uid="{7BBB8307-26C1-4A6B-A11B-C046A9E889A3}"/>
+    <hyperlink ref="I33" r:id="rId26" xr:uid="{90B349C4-33E9-4C05-A37C-6D393BD1852A}"/>
+    <hyperlink ref="I34" r:id="rId27" xr:uid="{B4B1FB19-A42A-409A-B51B-5F25103A0C02}"/>
+    <hyperlink ref="I35" r:id="rId28" xr:uid="{F2225EC5-E8B7-4715-A3DD-E8C926AFFBE9}"/>
+    <hyperlink ref="I36" r:id="rId29" xr:uid="{3191F546-109F-40A5-B0B8-48A63054C6DC}"/>
+    <hyperlink ref="I38" r:id="rId30" xr:uid="{7F488FF9-D4C9-4DFD-B169-AAE599D57542}"/>
+    <hyperlink ref="I39" r:id="rId31" xr:uid="{5A6D8735-3851-4571-89F6-B6E871265ABD}"/>
+    <hyperlink ref="I40" r:id="rId32" xr:uid="{8F6B8108-DD3C-4289-A467-451C85593211}"/>
+    <hyperlink ref="I42" r:id="rId33" xr:uid="{3F17C56B-6F35-4988-8883-DE8FFF7E7326}"/>
+    <hyperlink ref="I43" r:id="rId34" xr:uid="{636CA437-ACF7-4C88-BDF0-0C4D90586AB3}"/>
+    <hyperlink ref="I44" r:id="rId35" xr:uid="{8D18B240-303A-4DA2-881B-EEB25165E0A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="portrait" r:id="rId41"/>
+  <pageSetup scale="91" orientation="portrait" r:id="rId36"/>
   <ignoredErrors>
     <ignoredError sqref="A38 A41 A44 A47" formula="1"/>
   </ignoredErrors>

--- a/courses/Reg/DailyRecord.xlsx
+++ b/courses/Reg/DailyRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hbarreto\Documents\GitHub\homepage\courses\Reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA7373B-C5AB-4875-8D2B-570DDA67DF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB97B26-3666-4D1A-9F0C-FEE0E4647308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>LINEST and Solver</t>
   </si>
   <si>
-    <t>Interpreting Regression and Coefficients</t>
-  </si>
-  <si>
     <t>Predict Y; slope; vertical strips</t>
   </si>
   <si>
@@ -102,13 +99,7 @@
     <t>3D plot and plane</t>
   </si>
   <si>
-    <t>Monte Carlo Simulation and MC Sim Add-in</t>
-  </si>
-  <si>
     <t>Three SEs of sample average</t>
-  </si>
-  <si>
-    <t>Estimating Unemployment and the CPS</t>
   </si>
   <si>
     <t>Unem.xls</t>
@@ -238,9 +229,6 @@
   </si>
   <si>
     <t>Use colab, Google sheets, BIVARNORMAL</t>
-  </si>
-  <si>
-    <t>Multiple Regression Omitted Variable Bias</t>
   </si>
   <si>
     <t>6.OVB, OVB Rule w/ indep Xs</t>
@@ -911,6 +899,18 @@
   </si>
   <si>
     <t>copy/paste just the passcode itself</t>
+  </si>
+  <si>
+    <t>Estimating Unemployment via CPS</t>
+  </si>
+  <si>
+    <t>Monte Carlo Simulation and MCSim Add-in</t>
+  </si>
+  <si>
+    <t>Multiple Regression and Omitted Variable Bias</t>
+  </si>
+  <si>
+    <t>Interpreting Regression and its Coefficients</t>
   </si>
 </sst>
 </file>
@@ -1522,17 +1522,17 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
       <c r="A1" s="11" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="5"/>
       <c r="E1" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="13.2">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1540,11 +1540,11 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="24" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.2" thickBot="1">
@@ -1564,16 +1564,16 @@
         <v>12</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J4" s="28"/>
     </row>
@@ -1589,28 +1589,28 @@
         <v>Mon</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.6">
@@ -1632,19 +1632,19 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="24">
@@ -1666,19 +1666,19 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.6">
@@ -1694,25 +1694,25 @@
         <v>Mon</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
       <c r="F8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.6">
@@ -1728,25 +1728,25 @@
         <v>Wed</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.6">
@@ -1762,25 +1762,25 @@
         <v>Fri</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>55</v>
+        <v>255</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.6">
@@ -1796,25 +1796,25 @@
         <v>Mon</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.6">
@@ -1830,25 +1830,25 @@
         <v>Wed</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F12" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" t="s">
+        <v>157</v>
+      </c>
+      <c r="I12" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="G12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" t="s">
-        <v>161</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>163</v>
-      </c>
       <c r="J12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.6">
@@ -1864,25 +1864,25 @@
         <v>Fri</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6">
@@ -1898,25 +1898,25 @@
         <v>Mon</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.6">
@@ -1932,25 +1932,25 @@
         <v>Wed</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.6">
@@ -1966,25 +1966,25 @@
         <v>Fri</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J16" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.6">
@@ -2000,22 +2000,22 @@
         <v>Mon</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.6">
@@ -2034,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G18" s="6"/>
     </row>
@@ -2051,25 +2051,25 @@
         <v>Fri</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" t="s">
         <v>178</v>
       </c>
-      <c r="G19" t="s">
-        <v>182</v>
-      </c>
       <c r="H19" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.6">
@@ -2085,25 +2085,25 @@
         <v>Mon</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H20" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J20" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.6">
@@ -2119,25 +2119,25 @@
         <v>Wed</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J21" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.6">
@@ -2153,25 +2153,25 @@
         <v>Fri</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J22" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.6">
@@ -2187,25 +2187,25 @@
         <v>Mon</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F23" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H23" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J23" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.6">
@@ -2221,25 +2221,25 @@
         <v>Wed</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H24" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J24" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.6">
@@ -2255,25 +2255,25 @@
         <v>Fri</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F25" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G25" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H25" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J25" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.6">
@@ -2289,25 +2289,25 @@
         <v>Mon</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G26" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H26" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J26" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.6">
@@ -2323,25 +2323,25 @@
         <v>Wed</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F27" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J27" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.6">
@@ -2357,25 +2357,25 @@
         <v>Fri</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J28" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.6">
@@ -2389,7 +2389,7 @@
         <v>Mon</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.6">
@@ -2403,7 +2403,7 @@
         <v>Wed</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.6">
@@ -2417,7 +2417,7 @@
         <v>Fri</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.6">
@@ -2433,25 +2433,25 @@
         <v>Mon</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J32" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.6">
@@ -2467,25 +2467,25 @@
         <v>Wed</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H33" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J33" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.6">
@@ -2501,25 +2501,25 @@
         <v>Fri</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H34" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I34" s="27" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J34" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.6">
@@ -2535,25 +2535,25 @@
         <v>Mon</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E35" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F35" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G35" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H35" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I35" s="27" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J35" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15.6">
@@ -2569,22 +2569,22 @@
         <v>Wed</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I36" s="27" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J36" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1">
@@ -2603,13 +2603,13 @@
         <v>2</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.6">
@@ -2628,20 +2628,20 @@
         <v>10</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I38" s="27" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J38" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.6">
@@ -2660,13 +2660,13 @@
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I39" s="27" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J39" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15.6">
@@ -2682,19 +2682,19 @@
         <v>Fri</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H40" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I40" s="27" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J40" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15.6">
@@ -2710,13 +2710,13 @@
         <v>Mon</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.6">
@@ -2732,25 +2732,25 @@
         <v>Wed</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I42" s="27" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J42" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.6">
@@ -2766,19 +2766,19 @@
         <v>Fri</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G43" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H43" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I43" s="27" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J43" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.6">
@@ -2794,25 +2794,25 @@
         <v>Mon</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E44" t="s">
+        <v>115</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G44" t="s">
         <v>119</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G44" t="s">
-        <v>123</v>
-      </c>
       <c r="H44" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I44" s="27" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J44" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.6">
@@ -2828,13 +2828,13 @@
         <v>Wed</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.6">
@@ -2856,7 +2856,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G46" s="9"/>
     </row>
@@ -2873,10 +2873,10 @@
         <v>Mon</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>4</v>
@@ -2896,16 +2896,16 @@
         <v>Wed</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
         <v>8</v>
       </c>
       <c r="G48" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.4">
